--- a/customer-product/02-ACCOUNT-TRIGGER-TRACKER.xlsx
+++ b/customer-product/02-ACCOUNT-TRIGGER-TRACKER.xlsx
@@ -862,15 +862,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
@@ -885,7 +885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Eleven public signals. A trigger is an event, not a conclusion.</t>
+          <t>Sixteen public signals in four tiers. A trigger is an event, not a conclusion.</t>
         </is>
       </c>
     </row>
@@ -937,33 +937,33 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>New location</t>
+          <t>Contract out to bid</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>1 Buying</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>New Google Business Profile under an existing brand; 'now open' notices; local business press</t>
+          <t>State / county / city / school-district procurement portals. Set email alerts.</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Saw you opened the second location in August</t>
+          <t>Saw the custodial solicitation - are you taking bids from new vendors?</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>You'll need a cleaner there</t>
+          <t>Anything about the incumbent</t>
         </is>
       </c>
     </row>
@@ -973,33 +973,33 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>New facility / occupancy</t>
+          <t>Related services RFP</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>1 Buying</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Occupancy and tenant-improvement permits on your county or city portal</t>
+          <t>Same procurement portals - grounds, maintenance, facility services</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Saw the new building on Commerce cleared occupancy</t>
+          <t>Saw the facilities solicitation</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>You don't have a cleaner yet</t>
+          <t>That cleaning is also in play</t>
         </is>
       </c>
     </row>
@@ -1009,33 +1009,33 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Move / relocation</t>
+          <t>New facility / occupancy</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>90</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Address change on their Google listing; 'we've moved' notices; business press</t>
+          <t>Occupancy and tenant-improvement permits, county or city portal</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Noticed you moved to Commerce Street</t>
+          <t>Saw the new building cleared occupancy</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Your old cleaner won't follow you</t>
+          <t>You don't have a cleaner yet</t>
         </is>
       </c>
     </row>
@@ -1045,33 +1045,33 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Property management change</t>
+          <t>New location</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Portfolio pages on management company sites; listing management changes</t>
+          <t>New Google listing under an existing brand; 'now open' notices</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Saw you picked up the Elm Street building</t>
+          <t>Saw you opened the second location</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>The inherited vendor won't work out</t>
+          <t>You'll need a cleaner there</t>
         </is>
       </c>
     </row>
@@ -1081,33 +1081,33 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Facilities or ops hiring</t>
+          <t>Move / relocation</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>90</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Indeed and LinkedIn: Facilities Manager, Office Manager, Operations Manager</t>
+          <t>Address change on their Google listing; 'we've moved' notices</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Saw you're hiring a facilities manager</t>
+          <t>Noticed you moved to Commerce Street</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>They'll want to replace their vendors</t>
+          <t>Your old cleaner won't follow you</t>
         </is>
       </c>
     </row>
@@ -1117,33 +1117,33 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Renovation / reopening</t>
+          <t>New commercial lease</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Renovation permits; reopening notices; temporary closure on their listing</t>
+          <t>CRE listing flips from available to leased</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Saw the renovation permit for the Oak Street site</t>
+          <t>Saw you took the space on Commerce</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>You'll need post-construction cleaning</t>
+          <t>Anything about their vendor</t>
         </is>
       </c>
     </row>
@@ -1153,33 +1153,33 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Suite expansion</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Local business journals; press releases; state business registries</t>
+          <t>Listing changes; updated sq ft; a second suite number</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Saw the acquisition announcement last month</t>
+          <t>Saw you took the unit next door</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>They'll be consolidating vendors</t>
+          <t>Their cleaner can't handle it</t>
         </is>
       </c>
     </row>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Headcount growth</t>
+          <t>Competitor closing</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Several open roles at one address</t>
+          <t>A cleaning company's listing goes permanently closed; business-for-sale listings</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Looks like you're growing the team there</t>
+          <t>I understand you may be looking for a new provider</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>More staff means you need us</t>
+          <t>The competitor's name, or why they closed</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Funding / news</t>
+          <t>Post-construction complete</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2 Facility</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Local business journals</t>
+          <t>Permit portal, filtered to finaled commercial permits</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Saw the announcement</t>
+          <t>Saw the build finished on Oak Street</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>You have budget now</t>
+          <t>That you're the obvious choice</t>
         </is>
       </c>
     </row>
@@ -1261,33 +1261,33 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Property management change</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>3 Organizational</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Anything public, dated, and specific</t>
+          <t>Portfolio pages on management company sites; signage</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>State exactly what you observed</t>
+          <t>Saw you picked up the Elm Street building</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Anything you inferred from it</t>
+          <t>The inherited vendor won't work out</t>
         </is>
       </c>
     </row>
@@ -1297,135 +1297,415 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Review mentions cleaning</t>
+          <t>Building sold</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>3 Organizational</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>County property records</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Saw the building changed hands in July</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>New owners will want to cut costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Facilities or ops hiring</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>3 Organizational</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Indeed / LinkedIn: Facilities, Office, Operations Manager</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Saw you're hiring a facilities manager</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>They'll want to replace their vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Renovation / reopening</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>3 Organizational</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Renovation permits; reopening notices; temporary closure</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Saw the renovation permit for Oak Street</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>You'll need post-construction cleaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Acquisition / licence / sign</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>3 Organizational</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Business journals; city licence records; sign permits</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Saw the new signage went up</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Anything you inferred from it</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>New provider joining</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>3 Organizational</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Staff pages on medical and dental sites</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Saw Dr Chen joined the practice</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>That you know their workload changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Secondary signal</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>4 Secondary</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E19" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Public reviews mentioning cleanliness</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Nothing. Do not reference a review</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Anything at all — see the note below</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Why review mentions score 1, not 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>A review saying the restrooms were dirty feels like the strongest signal on this page. It isn't.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>It does not tell you the business controls the cleaning contract, that the reviewer was an employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>rather than a customer, that the problem is current, or that anyone is looking. It is an inference</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>about dissatisfaction, not an observation of a purchase window.</t>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Headcount, funding, reopening, seasonal, review mentions</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Nothing on its own - use to break a tie</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Anything, especially about reviews</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Use it to break a tie between two accounts that already have a real event. Never quote it to a</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>The four tiers</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>prospect — it reads as surveillance, and it asserts something about their vendor you cannot support.</t>
+          <t>Tier 1 Buying event - they have said in public that they are buying. Only procurement does this.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Facility event - a building changed in a way that creates a need.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Why the last column exists</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3 Organizational event - the organization changed; vendors MAY come up for review.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Everything in it is a conclusion. You saw a permit. You did not see their contract.</t>
+          <t>Tier 4 Secondary signal - activity, not evidence. Use to break a tie.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>State the event and offer to help. That is a legitimate reason to make contact, and it holds up</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>when someone asks how you found them.</t>
+          <t>Tier 1 breaks ties. A boosted facility event can reach 5, but a stated solicitation is a</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>different kind of knowledge.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Freshness</t>
-        </is>
-      </c>
+      <c r="B30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>The window is how long the event stays worth mentioning. Past it, referencing it reads as careless.</t>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Before you spend an hour on a public bid</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Confirm it is current, check the closing date, and check whether you can bid at all -</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>registration, bonding, insurance minimums, licensing, sometimes years trading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Check for prevailing wage: it changes your labour cost completely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Read the whole scope, and check whether a walkthrough is mandatory. Missing it disqualifies you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Public contracts are often price-driven and lower margin. Some are not worth winning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Why review mentions score 1, not 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>A review saying the restrooms were dirty feels like the strongest signal on this page. It isn't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>It does not tell you the business controls the cleaning contract, that the reviewer was an employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>rather than a customer, that the problem is current, or that anyone is looking. It is an inference</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>about dissatisfaction, not an observation of a purchase window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Use it to break a tie between two accounts that already have a real event. Never quote it to a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>prospect — it reads as surveillance, and it asserts something about their vendor you cannot support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Why the last column exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Everything in it is a conclusion. You saw a permit. You did not see their contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>State the event and offer to help. That is a legitimate reason to make contact, and it holds up</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>when someone asks how you found them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Freshness</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>The window is how long the event stays worth mentioning. Past it, referencing it reads as careless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Work the freshest first. That is the whole advantage this gives you over a list.</t>
         </is>
@@ -2255,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2291,7 +2571,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>New location</t>
+          <t>Contract out to bid</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -2358,7 +2638,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>New facility / occupancy</t>
+          <t>Related services RFP</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2425,7 +2705,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Move / relocation</t>
+          <t>New facility / occupancy</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2482,7 +2762,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Property management change</t>
+          <t>New location</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2534,7 +2814,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Facilities or ops hiring</t>
+          <t>Move / relocation</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2581,7 +2861,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Renovation / reopening</t>
+          <t>New commercial lease</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2618,7 +2898,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Suite expansion</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2655,7 +2935,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Headcount growth</t>
+          <t>Competitor closing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2692,7 +2972,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Funding / news</t>
+          <t>Post-construction complete</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2719,7 +2999,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Property management change</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2734,6 +3014,11 @@
           <t>Lost</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Building sold</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -2746,11 +3031,42 @@
           <t>Nurture</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Facilities or ops hiring</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
           <t>Disqualified</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Renovation / reopening</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Acquisition / licence / sign</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>New provider joining</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Secondary signal</t>
         </is>
       </c>
     </row>
@@ -24686,11 +25002,11 @@
         </is>
       </c>
       <c r="E4" s="7">
-        <f>IF(D4="","",IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D4="","",IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F4" s="7">
-        <f>IF(OR(D4="",H4="",I4=""),0,IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D4="",H4="",I4=""),0,IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -24712,7 +25028,7 @@
         <v/>
       </c>
       <c r="K4" s="7">
-        <f>IF(D4="","",IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D4="","",IFERROR(VLOOKUP(D4,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L4" s="7">
@@ -24742,11 +25058,11 @@
         </is>
       </c>
       <c r="E5" s="7">
-        <f>IF(D5="","",IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D5="","",IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>IF(OR(D5="",H5="",I5=""),0,IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D5="",H5="",I5=""),0,IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -24768,7 +25084,7 @@
         <v/>
       </c>
       <c r="K5" s="7">
-        <f>IF(D5="","",IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D5="","",IFERROR(VLOOKUP(D5,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L5" s="7">
@@ -24798,11 +25114,11 @@
         </is>
       </c>
       <c r="E6" s="7">
-        <f>IF(D6="","",IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D6="","",IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>IF(OR(D6="",H6="",I6=""),0,IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D6="",H6="",I6=""),0,IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -24824,7 +25140,7 @@
         <v/>
       </c>
       <c r="K6" s="7">
-        <f>IF(D6="","",IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D6="","",IFERROR(VLOOKUP(D6,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L6" s="7">
@@ -24838,11 +25154,11 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="9">
-        <f>IF(D7="","",IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D7="","",IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>IF(OR(D7="",H7="",I7=""),0,IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D7="",H7="",I7=""),0,IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G7" s="7" t="n"/>
@@ -24853,7 +25169,7 @@
         <v/>
       </c>
       <c r="K7" s="9">
-        <f>IF(D7="","",IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D7="","",IFERROR(VLOOKUP(D7,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L7" s="9">
@@ -24867,11 +25183,11 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="9">
-        <f>IF(D8="","",IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D8="","",IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IF(OR(D8="",H8="",I8=""),0,IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D8="",H8="",I8=""),0,IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G8" s="7" t="n"/>
@@ -24882,7 +25198,7 @@
         <v/>
       </c>
       <c r="K8" s="9">
-        <f>IF(D8="","",IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D8="","",IFERROR(VLOOKUP(D8,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L8" s="9">
@@ -24896,11 +25212,11 @@
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="9">
-        <f>IF(D9="","",IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D9="","",IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IF(OR(D9="",H9="",I9=""),0,IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D9="",H9="",I9=""),0,IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G9" s="7" t="n"/>
@@ -24911,7 +25227,7 @@
         <v/>
       </c>
       <c r="K9" s="9">
-        <f>IF(D9="","",IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D9="","",IFERROR(VLOOKUP(D9,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L9" s="9">
@@ -24925,11 +25241,11 @@
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="9">
-        <f>IF(D10="","",IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D10="","",IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IF(OR(D10="",H10="",I10=""),0,IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D10="",H10="",I10=""),0,IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G10" s="7" t="n"/>
@@ -24940,7 +25256,7 @@
         <v/>
       </c>
       <c r="K10" s="9">
-        <f>IF(D10="","",IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D10="","",IFERROR(VLOOKUP(D10,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L10" s="9">
@@ -24954,11 +25270,11 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="9">
-        <f>IF(D11="","",IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D11="","",IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IF(OR(D11="",H11="",I11=""),0,IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D11="",H11="",I11=""),0,IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -24969,7 +25285,7 @@
         <v/>
       </c>
       <c r="K11" s="9">
-        <f>IF(D11="","",IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D11="","",IFERROR(VLOOKUP(D11,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L11" s="9">
@@ -24983,11 +25299,11 @@
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="9">
-        <f>IF(D12="","",IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D12="","",IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IF(OR(D12="",H12="",I12=""),0,IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D12="",H12="",I12=""),0,IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G12" s="7" t="n"/>
@@ -24998,7 +25314,7 @@
         <v/>
       </c>
       <c r="K12" s="9">
-        <f>IF(D12="","",IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D12="","",IFERROR(VLOOKUP(D12,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L12" s="9">
@@ -25012,11 +25328,11 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="9">
-        <f>IF(D13="","",IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D13="","",IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IF(OR(D13="",H13="",I13=""),0,IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D13="",H13="",I13=""),0,IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G13" s="7" t="n"/>
@@ -25027,7 +25343,7 @@
         <v/>
       </c>
       <c r="K13" s="9">
-        <f>IF(D13="","",IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D13="","",IFERROR(VLOOKUP(D13,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L13" s="9">
@@ -25041,11 +25357,11 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="9">
-        <f>IF(D14="","",IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D14="","",IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>IF(OR(D14="",H14="",I14=""),0,IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D14="",H14="",I14=""),0,IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G14" s="7" t="n"/>
@@ -25056,7 +25372,7 @@
         <v/>
       </c>
       <c r="K14" s="9">
-        <f>IF(D14="","",IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D14="","",IFERROR(VLOOKUP(D14,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L14" s="9">
@@ -25070,11 +25386,11 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="9">
-        <f>IF(D15="","",IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D15="","",IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>IF(OR(D15="",H15="",I15=""),0,IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D15="",H15="",I15=""),0,IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G15" s="7" t="n"/>
@@ -25085,7 +25401,7 @@
         <v/>
       </c>
       <c r="K15" s="9">
-        <f>IF(D15="","",IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D15="","",IFERROR(VLOOKUP(D15,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L15" s="9">
@@ -25099,11 +25415,11 @@
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="9">
-        <f>IF(D16="","",IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D16="","",IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>IF(OR(D16="",H16="",I16=""),0,IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D16="",H16="",I16=""),0,IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G16" s="7" t="n"/>
@@ -25114,7 +25430,7 @@
         <v/>
       </c>
       <c r="K16" s="9">
-        <f>IF(D16="","",IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D16="","",IFERROR(VLOOKUP(D16,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L16" s="9">
@@ -25128,11 +25444,11 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="9">
-        <f>IF(D17="","",IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D17="","",IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>IF(OR(D17="",H17="",I17=""),0,IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D17="",H17="",I17=""),0,IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G17" s="7" t="n"/>
@@ -25143,7 +25459,7 @@
         <v/>
       </c>
       <c r="K17" s="9">
-        <f>IF(D17="","",IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D17="","",IFERROR(VLOOKUP(D17,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L17" s="9">
@@ -25157,11 +25473,11 @@
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="9">
-        <f>IF(D18="","",IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D18="","",IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>IF(OR(D18="",H18="",I18=""),0,IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D18="",H18="",I18=""),0,IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G18" s="7" t="n"/>
@@ -25172,7 +25488,7 @@
         <v/>
       </c>
       <c r="K18" s="9">
-        <f>IF(D18="","",IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D18="","",IFERROR(VLOOKUP(D18,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L18" s="9">
@@ -25186,11 +25502,11 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="9">
-        <f>IF(D19="","",IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D19="","",IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>IF(OR(D19="",H19="",I19=""),0,IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D19="",H19="",I19=""),0,IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G19" s="7" t="n"/>
@@ -25201,7 +25517,7 @@
         <v/>
       </c>
       <c r="K19" s="9">
-        <f>IF(D19="","",IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D19="","",IFERROR(VLOOKUP(D19,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L19" s="9">
@@ -25215,11 +25531,11 @@
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="9">
-        <f>IF(D20="","",IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D20="","",IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>IF(OR(D20="",H20="",I20=""),0,IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D20="",H20="",I20=""),0,IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G20" s="7" t="n"/>
@@ -25230,7 +25546,7 @@
         <v/>
       </c>
       <c r="K20" s="9">
-        <f>IF(D20="","",IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D20="","",IFERROR(VLOOKUP(D20,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L20" s="9">
@@ -25244,11 +25560,11 @@
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="9">
-        <f>IF(D21="","",IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D21="","",IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>IF(OR(D21="",H21="",I21=""),0,IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D21="",H21="",I21=""),0,IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G21" s="7" t="n"/>
@@ -25259,7 +25575,7 @@
         <v/>
       </c>
       <c r="K21" s="9">
-        <f>IF(D21="","",IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D21="","",IFERROR(VLOOKUP(D21,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L21" s="9">
@@ -25273,11 +25589,11 @@
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="9">
-        <f>IF(D22="","",IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D22="","",IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>IF(OR(D22="",H22="",I22=""),0,IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D22="",H22="",I22=""),0,IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -25288,7 +25604,7 @@
         <v/>
       </c>
       <c r="K22" s="9">
-        <f>IF(D22="","",IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D22="","",IFERROR(VLOOKUP(D22,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L22" s="9">
@@ -25302,11 +25618,11 @@
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="9">
-        <f>IF(D23="","",IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D23="","",IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>IF(OR(D23="",H23="",I23=""),0,IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D23="",H23="",I23=""),0,IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -25317,7 +25633,7 @@
         <v/>
       </c>
       <c r="K23" s="9">
-        <f>IF(D23="","",IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D23="","",IFERROR(VLOOKUP(D23,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L23" s="9">
@@ -25331,11 +25647,11 @@
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="9">
-        <f>IF(D24="","",IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D24="","",IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>IF(OR(D24="",H24="",I24=""),0,IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D24="",H24="",I24=""),0,IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G24" s="7" t="n"/>
@@ -25346,7 +25662,7 @@
         <v/>
       </c>
       <c r="K24" s="9">
-        <f>IF(D24="","",IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D24="","",IFERROR(VLOOKUP(D24,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L24" s="9">
@@ -25360,11 +25676,11 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="9">
-        <f>IF(D25="","",IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D25="","",IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>IF(OR(D25="",H25="",I25=""),0,IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D25="",H25="",I25=""),0,IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -25375,7 +25691,7 @@
         <v/>
       </c>
       <c r="K25" s="9">
-        <f>IF(D25="","",IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D25="","",IFERROR(VLOOKUP(D25,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L25" s="9">
@@ -25389,11 +25705,11 @@
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="9">
-        <f>IF(D26="","",IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D26="","",IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>IF(OR(D26="",H26="",I26=""),0,IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D26="",H26="",I26=""),0,IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -25404,7 +25720,7 @@
         <v/>
       </c>
       <c r="K26" s="9">
-        <f>IF(D26="","",IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D26="","",IFERROR(VLOOKUP(D26,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L26" s="9">
@@ -25418,11 +25734,11 @@
       <c r="C27" s="7" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="9">
-        <f>IF(D27="","",IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D27="","",IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>IF(OR(D27="",H27="",I27=""),0,IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D27="",H27="",I27=""),0,IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G27" s="7" t="n"/>
@@ -25433,7 +25749,7 @@
         <v/>
       </c>
       <c r="K27" s="9">
-        <f>IF(D27="","",IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D27="","",IFERROR(VLOOKUP(D27,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L27" s="9">
@@ -25447,11 +25763,11 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="9">
-        <f>IF(D28="","",IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D28="","",IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>IF(OR(D28="",H28="",I28=""),0,IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D28="",H28="",I28=""),0,IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G28" s="7" t="n"/>
@@ -25462,7 +25778,7 @@
         <v/>
       </c>
       <c r="K28" s="9">
-        <f>IF(D28="","",IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D28="","",IFERROR(VLOOKUP(D28,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L28" s="9">
@@ -25476,11 +25792,11 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="9">
-        <f>IF(D29="","",IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D29="","",IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F29" s="9">
-        <f>IF(OR(D29="",H29="",I29=""),0,IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D29="",H29="",I29=""),0,IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G29" s="7" t="n"/>
@@ -25491,7 +25807,7 @@
         <v/>
       </c>
       <c r="K29" s="9">
-        <f>IF(D29="","",IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D29="","",IFERROR(VLOOKUP(D29,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L29" s="9">
@@ -25505,11 +25821,11 @@
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="9">
-        <f>IF(D30="","",IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D30="","",IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F30" s="9">
-        <f>IF(OR(D30="",H30="",I30=""),0,IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D30="",H30="",I30=""),0,IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G30" s="7" t="n"/>
@@ -25520,7 +25836,7 @@
         <v/>
       </c>
       <c r="K30" s="9">
-        <f>IF(D30="","",IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D30="","",IFERROR(VLOOKUP(D30,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L30" s="9">
@@ -25534,11 +25850,11 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="9">
-        <f>IF(D31="","",IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D31="","",IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F31" s="9">
-        <f>IF(OR(D31="",H31="",I31=""),0,IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D31="",H31="",I31=""),0,IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G31" s="7" t="n"/>
@@ -25549,7 +25865,7 @@
         <v/>
       </c>
       <c r="K31" s="9">
-        <f>IF(D31="","",IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D31="","",IFERROR(VLOOKUP(D31,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L31" s="9">
@@ -25563,11 +25879,11 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="9">
-        <f>IF(D32="","",IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D32="","",IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F32" s="9">
-        <f>IF(OR(D32="",H32="",I32=""),0,IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D32="",H32="",I32=""),0,IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G32" s="7" t="n"/>
@@ -25578,7 +25894,7 @@
         <v/>
       </c>
       <c r="K32" s="9">
-        <f>IF(D32="","",IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D32="","",IFERROR(VLOOKUP(D32,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L32" s="9">
@@ -25592,11 +25908,11 @@
       <c r="C33" s="7" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="9">
-        <f>IF(D33="","",IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D33="","",IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F33" s="9">
-        <f>IF(OR(D33="",H33="",I33=""),0,IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D33="",H33="",I33=""),0,IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G33" s="7" t="n"/>
@@ -25607,7 +25923,7 @@
         <v/>
       </c>
       <c r="K33" s="9">
-        <f>IF(D33="","",IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D33="","",IFERROR(VLOOKUP(D33,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L33" s="9">
@@ -25621,11 +25937,11 @@
       <c r="C34" s="7" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="9">
-        <f>IF(D34="","",IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D34="","",IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F34" s="9">
-        <f>IF(OR(D34="",H34="",I34=""),0,IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D34="",H34="",I34=""),0,IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G34" s="7" t="n"/>
@@ -25636,7 +25952,7 @@
         <v/>
       </c>
       <c r="K34" s="9">
-        <f>IF(D34="","",IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D34="","",IFERROR(VLOOKUP(D34,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L34" s="9">
@@ -25650,11 +25966,11 @@
       <c r="C35" s="7" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="9">
-        <f>IF(D35="","",IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D35="","",IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F35" s="9">
-        <f>IF(OR(D35="",H35="",I35=""),0,IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D35="",H35="",I35=""),0,IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G35" s="7" t="n"/>
@@ -25665,7 +25981,7 @@
         <v/>
       </c>
       <c r="K35" s="9">
-        <f>IF(D35="","",IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D35="","",IFERROR(VLOOKUP(D35,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L35" s="9">
@@ -25679,11 +25995,11 @@
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="9">
-        <f>IF(D36="","",IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D36="","",IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F36" s="9">
-        <f>IF(OR(D36="",H36="",I36=""),0,IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D36="",H36="",I36=""),0,IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G36" s="7" t="n"/>
@@ -25694,7 +26010,7 @@
         <v/>
       </c>
       <c r="K36" s="9">
-        <f>IF(D36="","",IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D36="","",IFERROR(VLOOKUP(D36,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L36" s="9">
@@ -25708,11 +26024,11 @@
       <c r="C37" s="7" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="9">
-        <f>IF(D37="","",IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D37="","",IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F37" s="9">
-        <f>IF(OR(D37="",H37="",I37=""),0,IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D37="",H37="",I37=""),0,IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -25723,7 +26039,7 @@
         <v/>
       </c>
       <c r="K37" s="9">
-        <f>IF(D37="","",IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D37="","",IFERROR(VLOOKUP(D37,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L37" s="9">
@@ -25737,11 +26053,11 @@
       <c r="C38" s="7" t="n"/>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="9">
-        <f>IF(D38="","",IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D38="","",IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F38" s="9">
-        <f>IF(OR(D38="",H38="",I38=""),0,IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D38="",H38="",I38=""),0,IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G38" s="7" t="n"/>
@@ -25752,7 +26068,7 @@
         <v/>
       </c>
       <c r="K38" s="9">
-        <f>IF(D38="","",IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D38="","",IFERROR(VLOOKUP(D38,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L38" s="9">
@@ -25766,11 +26082,11 @@
       <c r="C39" s="7" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="9">
-        <f>IF(D39="","",IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D39="","",IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>IF(OR(D39="",H39="",I39=""),0,IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D39="",H39="",I39=""),0,IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G39" s="7" t="n"/>
@@ -25781,7 +26097,7 @@
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>IF(D39="","",IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D39="","",IFERROR(VLOOKUP(D39,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L39" s="9">
@@ -25795,11 +26111,11 @@
       <c r="C40" s="7" t="n"/>
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="9">
-        <f>IF(D40="","",IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D40="","",IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>IF(OR(D40="",H40="",I40=""),0,IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D40="",H40="",I40=""),0,IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G40" s="7" t="n"/>
@@ -25810,7 +26126,7 @@
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>IF(D40="","",IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D40="","",IFERROR(VLOOKUP(D40,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L40" s="9">
@@ -25824,11 +26140,11 @@
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="9">
-        <f>IF(D41="","",IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D41="","",IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F41" s="9">
-        <f>IF(OR(D41="",H41="",I41=""),0,IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D41="",H41="",I41=""),0,IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G41" s="7" t="n"/>
@@ -25839,7 +26155,7 @@
         <v/>
       </c>
       <c r="K41" s="9">
-        <f>IF(D41="","",IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D41="","",IFERROR(VLOOKUP(D41,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L41" s="9">
@@ -25853,11 +26169,11 @@
       <c r="C42" s="7" t="n"/>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="9">
-        <f>IF(D42="","",IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D42="","",IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F42" s="9">
-        <f>IF(OR(D42="",H42="",I42=""),0,IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D42="",H42="",I42=""),0,IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G42" s="7" t="n"/>
@@ -25868,7 +26184,7 @@
         <v/>
       </c>
       <c r="K42" s="9">
-        <f>IF(D42="","",IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D42="","",IFERROR(VLOOKUP(D42,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L42" s="9">
@@ -25882,11 +26198,11 @@
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="9">
-        <f>IF(D43="","",IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D43="","",IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F43" s="9">
-        <f>IF(OR(D43="",H43="",I43=""),0,IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D43="",H43="",I43=""),0,IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G43" s="7" t="n"/>
@@ -25897,7 +26213,7 @@
         <v/>
       </c>
       <c r="K43" s="9">
-        <f>IF(D43="","",IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D43="","",IFERROR(VLOOKUP(D43,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L43" s="9">
@@ -25911,11 +26227,11 @@
       <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="9">
-        <f>IF(D44="","",IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D44="","",IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F44" s="9">
-        <f>IF(OR(D44="",H44="",I44=""),0,IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D44="",H44="",I44=""),0,IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G44" s="7" t="n"/>
@@ -25926,7 +26242,7 @@
         <v/>
       </c>
       <c r="K44" s="9">
-        <f>IF(D44="","",IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D44="","",IFERROR(VLOOKUP(D44,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L44" s="9">
@@ -25940,11 +26256,11 @@
       <c r="C45" s="7" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="9">
-        <f>IF(D45="","",IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D45="","",IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F45" s="9">
-        <f>IF(OR(D45="",H45="",I45=""),0,IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D45="",H45="",I45=""),0,IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G45" s="7" t="n"/>
@@ -25955,7 +26271,7 @@
         <v/>
       </c>
       <c r="K45" s="9">
-        <f>IF(D45="","",IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D45="","",IFERROR(VLOOKUP(D45,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L45" s="9">
@@ -25969,11 +26285,11 @@
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="9">
-        <f>IF(D46="","",IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D46="","",IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F46" s="9">
-        <f>IF(OR(D46="",H46="",I46=""),0,IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D46="",H46="",I46=""),0,IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G46" s="7" t="n"/>
@@ -25984,7 +26300,7 @@
         <v/>
       </c>
       <c r="K46" s="9">
-        <f>IF(D46="","",IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D46="","",IFERROR(VLOOKUP(D46,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L46" s="9">
@@ -25998,11 +26314,11 @@
       <c r="C47" s="7" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="9">
-        <f>IF(D47="","",IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D47="","",IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F47" s="9">
-        <f>IF(OR(D47="",H47="",I47=""),0,IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D47="",H47="",I47=""),0,IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G47" s="7" t="n"/>
@@ -26013,7 +26329,7 @@
         <v/>
       </c>
       <c r="K47" s="9">
-        <f>IF(D47="","",IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D47="","",IFERROR(VLOOKUP(D47,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L47" s="9">
@@ -26027,11 +26343,11 @@
       <c r="C48" s="7" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="9">
-        <f>IF(D48="","",IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D48="","",IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F48" s="9">
-        <f>IF(OR(D48="",H48="",I48=""),0,IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D48="",H48="",I48=""),0,IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G48" s="7" t="n"/>
@@ -26042,7 +26358,7 @@
         <v/>
       </c>
       <c r="K48" s="9">
-        <f>IF(D48="","",IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D48="","",IFERROR(VLOOKUP(D48,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L48" s="9">
@@ -26056,11 +26372,11 @@
       <c r="C49" s="7" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="9">
-        <f>IF(D49="","",IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D49="","",IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F49" s="9">
-        <f>IF(OR(D49="",H49="",I49=""),0,IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D49="",H49="",I49=""),0,IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G49" s="7" t="n"/>
@@ -26071,7 +26387,7 @@
         <v/>
       </c>
       <c r="K49" s="9">
-        <f>IF(D49="","",IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D49="","",IFERROR(VLOOKUP(D49,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L49" s="9">
@@ -26085,11 +26401,11 @@
       <c r="C50" s="7" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="9">
-        <f>IF(D50="","",IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D50="","",IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F50" s="9">
-        <f>IF(OR(D50="",H50="",I50=""),0,IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D50="",H50="",I50=""),0,IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G50" s="7" t="n"/>
@@ -26100,7 +26416,7 @@
         <v/>
       </c>
       <c r="K50" s="9">
-        <f>IF(D50="","",IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D50="","",IFERROR(VLOOKUP(D50,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L50" s="9">
@@ -26114,11 +26430,11 @@
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="9">
-        <f>IF(D51="","",IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D51="","",IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F51" s="9">
-        <f>IF(OR(D51="",H51="",I51=""),0,IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D51="",H51="",I51=""),0,IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G51" s="7" t="n"/>
@@ -26129,7 +26445,7 @@
         <v/>
       </c>
       <c r="K51" s="9">
-        <f>IF(D51="","",IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D51="","",IFERROR(VLOOKUP(D51,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L51" s="9">
@@ -26143,11 +26459,11 @@
       <c r="C52" s="7" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="9">
-        <f>IF(D52="","",IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D52="","",IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F52" s="9">
-        <f>IF(OR(D52="",H52="",I52=""),0,IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D52="",H52="",I52=""),0,IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -26158,7 +26474,7 @@
         <v/>
       </c>
       <c r="K52" s="9">
-        <f>IF(D52="","",IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D52="","",IFERROR(VLOOKUP(D52,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L52" s="9">
@@ -26172,11 +26488,11 @@
       <c r="C53" s="7" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="9">
-        <f>IF(D53="","",IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D53="","",IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F53" s="9">
-        <f>IF(OR(D53="",H53="",I53=""),0,IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D53="",H53="",I53=""),0,IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -26187,7 +26503,7 @@
         <v/>
       </c>
       <c r="K53" s="9">
-        <f>IF(D53="","",IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D53="","",IFERROR(VLOOKUP(D53,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L53" s="9">
@@ -26201,11 +26517,11 @@
       <c r="C54" s="7" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="9">
-        <f>IF(D54="","",IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D54="","",IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F54" s="9">
-        <f>IF(OR(D54="",H54="",I54=""),0,IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D54="",H54="",I54=""),0,IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G54" s="7" t="n"/>
@@ -26216,7 +26532,7 @@
         <v/>
       </c>
       <c r="K54" s="9">
-        <f>IF(D54="","",IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D54="","",IFERROR(VLOOKUP(D54,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L54" s="9">
@@ -26230,11 +26546,11 @@
       <c r="C55" s="7" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="9">
-        <f>IF(D55="","",IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D55="","",IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F55" s="9">
-        <f>IF(OR(D55="",H55="",I55=""),0,IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D55="",H55="",I55=""),0,IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -26245,7 +26561,7 @@
         <v/>
       </c>
       <c r="K55" s="9">
-        <f>IF(D55="","",IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D55="","",IFERROR(VLOOKUP(D55,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L55" s="9">
@@ -26259,11 +26575,11 @@
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="9">
-        <f>IF(D56="","",IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D56="","",IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F56" s="9">
-        <f>IF(OR(D56="",H56="",I56=""),0,IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D56="",H56="",I56=""),0,IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -26274,7 +26590,7 @@
         <v/>
       </c>
       <c r="K56" s="9">
-        <f>IF(D56="","",IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D56="","",IFERROR(VLOOKUP(D56,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L56" s="9">
@@ -26288,11 +26604,11 @@
       <c r="C57" s="7" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="9">
-        <f>IF(D57="","",IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D57="","",IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F57" s="9">
-        <f>IF(OR(D57="",H57="",I57=""),0,IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D57="",H57="",I57=""),0,IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G57" s="7" t="n"/>
@@ -26303,7 +26619,7 @@
         <v/>
       </c>
       <c r="K57" s="9">
-        <f>IF(D57="","",IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D57="","",IFERROR(VLOOKUP(D57,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L57" s="9">
@@ -26317,11 +26633,11 @@
       <c r="C58" s="7" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="9">
-        <f>IF(D58="","",IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D58="","",IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F58" s="9">
-        <f>IF(OR(D58="",H58="",I58=""),0,IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D58="",H58="",I58=""),0,IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G58" s="7" t="n"/>
@@ -26332,7 +26648,7 @@
         <v/>
       </c>
       <c r="K58" s="9">
-        <f>IF(D58="","",IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D58="","",IFERROR(VLOOKUP(D58,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L58" s="9">
@@ -26346,11 +26662,11 @@
       <c r="C59" s="7" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="9">
-        <f>IF(D59="","",IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D59="","",IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F59" s="9">
-        <f>IF(OR(D59="",H59="",I59=""),0,IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D59="",H59="",I59=""),0,IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G59" s="7" t="n"/>
@@ -26361,7 +26677,7 @@
         <v/>
       </c>
       <c r="K59" s="9">
-        <f>IF(D59="","",IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D59="","",IFERROR(VLOOKUP(D59,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L59" s="9">
@@ -26375,11 +26691,11 @@
       <c r="C60" s="7" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="9">
-        <f>IF(D60="","",IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D60="","",IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F60" s="9">
-        <f>IF(OR(D60="",H60="",I60=""),0,IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D60="",H60="",I60=""),0,IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G60" s="7" t="n"/>
@@ -26390,7 +26706,7 @@
         <v/>
       </c>
       <c r="K60" s="9">
-        <f>IF(D60="","",IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D60="","",IFERROR(VLOOKUP(D60,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L60" s="9">
@@ -26404,11 +26720,11 @@
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="9">
-        <f>IF(D61="","",IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D61="","",IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F61" s="9">
-        <f>IF(OR(D61="",H61="",I61=""),0,IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D61="",H61="",I61=""),0,IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G61" s="7" t="n"/>
@@ -26419,7 +26735,7 @@
         <v/>
       </c>
       <c r="K61" s="9">
-        <f>IF(D61="","",IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D61="","",IFERROR(VLOOKUP(D61,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L61" s="9">
@@ -26433,11 +26749,11 @@
       <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="9">
-        <f>IF(D62="","",IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D62="","",IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F62" s="9">
-        <f>IF(OR(D62="",H62="",I62=""),0,IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D62="",H62="",I62=""),0,IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G62" s="7" t="n"/>
@@ -26448,7 +26764,7 @@
         <v/>
       </c>
       <c r="K62" s="9">
-        <f>IF(D62="","",IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D62="","",IFERROR(VLOOKUP(D62,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L62" s="9">
@@ -26462,11 +26778,11 @@
       <c r="C63" s="7" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="9">
-        <f>IF(D63="","",IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D63="","",IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F63" s="9">
-        <f>IF(OR(D63="",H63="",I63=""),0,IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D63="",H63="",I63=""),0,IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G63" s="7" t="n"/>
@@ -26477,7 +26793,7 @@
         <v/>
       </c>
       <c r="K63" s="9">
-        <f>IF(D63="","",IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D63="","",IFERROR(VLOOKUP(D63,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L63" s="9">
@@ -26491,11 +26807,11 @@
       <c r="C64" s="7" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="9">
-        <f>IF(D64="","",IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D64="","",IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F64" s="9">
-        <f>IF(OR(D64="",H64="",I64=""),0,IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D64="",H64="",I64=""),0,IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G64" s="7" t="n"/>
@@ -26506,7 +26822,7 @@
         <v/>
       </c>
       <c r="K64" s="9">
-        <f>IF(D64="","",IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D64="","",IFERROR(VLOOKUP(D64,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L64" s="9">
@@ -26520,11 +26836,11 @@
       <c r="C65" s="7" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="9">
-        <f>IF(D65="","",IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D65="","",IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F65" s="9">
-        <f>IF(OR(D65="",H65="",I65=""),0,IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D65="",H65="",I65=""),0,IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -26535,7 +26851,7 @@
         <v/>
       </c>
       <c r="K65" s="9">
-        <f>IF(D65="","",IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D65="","",IFERROR(VLOOKUP(D65,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L65" s="9">
@@ -26549,11 +26865,11 @@
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="9">
-        <f>IF(D66="","",IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D66="","",IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F66" s="9">
-        <f>IF(OR(D66="",H66="",I66=""),0,IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D66="",H66="",I66=""),0,IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -26564,7 +26880,7 @@
         <v/>
       </c>
       <c r="K66" s="9">
-        <f>IF(D66="","",IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D66="","",IFERROR(VLOOKUP(D66,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L66" s="9">
@@ -26578,11 +26894,11 @@
       <c r="C67" s="7" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="9">
-        <f>IF(D67="","",IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D67="","",IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F67" s="9">
-        <f>IF(OR(D67="",H67="",I67=""),0,IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D67="",H67="",I67=""),0,IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G67" s="7" t="n"/>
@@ -26593,7 +26909,7 @@
         <v/>
       </c>
       <c r="K67" s="9">
-        <f>IF(D67="","",IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D67="","",IFERROR(VLOOKUP(D67,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L67" s="9">
@@ -26607,11 +26923,11 @@
       <c r="C68" s="7" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="9">
-        <f>IF(D68="","",IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D68="","",IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F68" s="9">
-        <f>IF(OR(D68="",H68="",I68=""),0,IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D68="",H68="",I68=""),0,IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G68" s="7" t="n"/>
@@ -26622,7 +26938,7 @@
         <v/>
       </c>
       <c r="K68" s="9">
-        <f>IF(D68="","",IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D68="","",IFERROR(VLOOKUP(D68,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L68" s="9">
@@ -26636,11 +26952,11 @@
       <c r="C69" s="7" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="9">
-        <f>IF(D69="","",IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D69="","",IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F69" s="9">
-        <f>IF(OR(D69="",H69="",I69=""),0,IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D69="",H69="",I69=""),0,IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G69" s="7" t="n"/>
@@ -26651,7 +26967,7 @@
         <v/>
       </c>
       <c r="K69" s="9">
-        <f>IF(D69="","",IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D69="","",IFERROR(VLOOKUP(D69,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L69" s="9">
@@ -26665,11 +26981,11 @@
       <c r="C70" s="7" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="9">
-        <f>IF(D70="","",IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D70="","",IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F70" s="9">
-        <f>IF(OR(D70="",H70="",I70=""),0,IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D70="",H70="",I70=""),0,IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G70" s="7" t="n"/>
@@ -26680,7 +26996,7 @@
         <v/>
       </c>
       <c r="K70" s="9">
-        <f>IF(D70="","",IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D70="","",IFERROR(VLOOKUP(D70,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L70" s="9">
@@ -26694,11 +27010,11 @@
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="9">
-        <f>IF(D71="","",IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D71="","",IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F71" s="9">
-        <f>IF(OR(D71="",H71="",I71=""),0,IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D71="",H71="",I71=""),0,IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G71" s="7" t="n"/>
@@ -26709,7 +27025,7 @@
         <v/>
       </c>
       <c r="K71" s="9">
-        <f>IF(D71="","",IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D71="","",IFERROR(VLOOKUP(D71,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L71" s="9">
@@ -26723,11 +27039,11 @@
       <c r="C72" s="7" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="9">
-        <f>IF(D72="","",IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D72="","",IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F72" s="9">
-        <f>IF(OR(D72="",H72="",I72=""),0,IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D72="",H72="",I72=""),0,IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G72" s="7" t="n"/>
@@ -26738,7 +27054,7 @@
         <v/>
       </c>
       <c r="K72" s="9">
-        <f>IF(D72="","",IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D72="","",IFERROR(VLOOKUP(D72,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L72" s="9">
@@ -26752,11 +27068,11 @@
       <c r="C73" s="7" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="9">
-        <f>IF(D73="","",IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D73="","",IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F73" s="9">
-        <f>IF(OR(D73="",H73="",I73=""),0,IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D73="",H73="",I73=""),0,IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G73" s="7" t="n"/>
@@ -26767,7 +27083,7 @@
         <v/>
       </c>
       <c r="K73" s="9">
-        <f>IF(D73="","",IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D73="","",IFERROR(VLOOKUP(D73,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L73" s="9">
@@ -26781,11 +27097,11 @@
       <c r="C74" s="7" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="9">
-        <f>IF(D74="","",IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D74="","",IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F74" s="9">
-        <f>IF(OR(D74="",H74="",I74=""),0,IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D74="",H74="",I74=""),0,IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G74" s="7" t="n"/>
@@ -26796,7 +27112,7 @@
         <v/>
       </c>
       <c r="K74" s="9">
-        <f>IF(D74="","",IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D74="","",IFERROR(VLOOKUP(D74,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L74" s="9">
@@ -26810,11 +27126,11 @@
       <c r="C75" s="7" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="9">
-        <f>IF(D75="","",IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D75="","",IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F75" s="9">
-        <f>IF(OR(D75="",H75="",I75=""),0,IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D75="",H75="",I75=""),0,IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -26825,7 +27141,7 @@
         <v/>
       </c>
       <c r="K75" s="9">
-        <f>IF(D75="","",IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D75="","",IFERROR(VLOOKUP(D75,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L75" s="9">
@@ -26839,11 +27155,11 @@
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="9">
-        <f>IF(D76="","",IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D76="","",IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F76" s="9">
-        <f>IF(OR(D76="",H76="",I76=""),0,IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D76="",H76="",I76=""),0,IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G76" s="7" t="n"/>
@@ -26854,7 +27170,7 @@
         <v/>
       </c>
       <c r="K76" s="9">
-        <f>IF(D76="","",IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D76="","",IFERROR(VLOOKUP(D76,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L76" s="9">
@@ -26868,11 +27184,11 @@
       <c r="C77" s="7" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="9">
-        <f>IF(D77="","",IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D77="","",IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F77" s="9">
-        <f>IF(OR(D77="",H77="",I77=""),0,IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D77="",H77="",I77=""),0,IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G77" s="7" t="n"/>
@@ -26883,7 +27199,7 @@
         <v/>
       </c>
       <c r="K77" s="9">
-        <f>IF(D77="","",IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D77="","",IFERROR(VLOOKUP(D77,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L77" s="9">
@@ -26897,11 +27213,11 @@
       <c r="C78" s="7" t="n"/>
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="9">
-        <f>IF(D78="","",IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D78="","",IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F78" s="9">
-        <f>IF(OR(D78="",H78="",I78=""),0,IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D78="",H78="",I78=""),0,IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G78" s="7" t="n"/>
@@ -26912,7 +27228,7 @@
         <v/>
       </c>
       <c r="K78" s="9">
-        <f>IF(D78="","",IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D78="","",IFERROR(VLOOKUP(D78,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L78" s="9">
@@ -26926,11 +27242,11 @@
       <c r="C79" s="7" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="9">
-        <f>IF(D79="","",IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D79="","",IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F79" s="9">
-        <f>IF(OR(D79="",H79="",I79=""),0,IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D79="",H79="",I79=""),0,IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G79" s="7" t="n"/>
@@ -26941,7 +27257,7 @@
         <v/>
       </c>
       <c r="K79" s="9">
-        <f>IF(D79="","",IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D79="","",IFERROR(VLOOKUP(D79,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L79" s="9">
@@ -26955,11 +27271,11 @@
       <c r="C80" s="7" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="9">
-        <f>IF(D80="","",IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D80="","",IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F80" s="9">
-        <f>IF(OR(D80="",H80="",I80=""),0,IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D80="",H80="",I80=""),0,IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G80" s="7" t="n"/>
@@ -26970,7 +27286,7 @@
         <v/>
       </c>
       <c r="K80" s="9">
-        <f>IF(D80="","",IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D80="","",IFERROR(VLOOKUP(D80,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L80" s="9">
@@ -26984,11 +27300,11 @@
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="9">
-        <f>IF(D81="","",IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D81="","",IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F81" s="9">
-        <f>IF(OR(D81="",H81="",I81=""),0,IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D81="",H81="",I81=""),0,IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G81" s="7" t="n"/>
@@ -26999,7 +27315,7 @@
         <v/>
       </c>
       <c r="K81" s="9">
-        <f>IF(D81="","",IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D81="","",IFERROR(VLOOKUP(D81,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L81" s="9">
@@ -27013,11 +27329,11 @@
       <c r="C82" s="7" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="9">
-        <f>IF(D82="","",IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D82="","",IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F82" s="9">
-        <f>IF(OR(D82="",H82="",I82=""),0,IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D82="",H82="",I82=""),0,IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G82" s="7" t="n"/>
@@ -27028,7 +27344,7 @@
         <v/>
       </c>
       <c r="K82" s="9">
-        <f>IF(D82="","",IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D82="","",IFERROR(VLOOKUP(D82,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L82" s="9">
@@ -27042,11 +27358,11 @@
       <c r="C83" s="7" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="9">
-        <f>IF(D83="","",IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D83="","",IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F83" s="9">
-        <f>IF(OR(D83="",H83="",I83=""),0,IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D83="",H83="",I83=""),0,IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G83" s="7" t="n"/>
@@ -27057,7 +27373,7 @@
         <v/>
       </c>
       <c r="K83" s="9">
-        <f>IF(D83="","",IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D83="","",IFERROR(VLOOKUP(D83,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L83" s="9">
@@ -27071,11 +27387,11 @@
       <c r="C84" s="7" t="n"/>
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="9">
-        <f>IF(D84="","",IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D84="","",IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F84" s="9">
-        <f>IF(OR(D84="",H84="",I84=""),0,IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D84="",H84="",I84=""),0,IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G84" s="7" t="n"/>
@@ -27086,7 +27402,7 @@
         <v/>
       </c>
       <c r="K84" s="9">
-        <f>IF(D84="","",IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D84="","",IFERROR(VLOOKUP(D84,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L84" s="9">
@@ -27100,11 +27416,11 @@
       <c r="C85" s="7" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="9">
-        <f>IF(D85="","",IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D85="","",IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F85" s="9">
-        <f>IF(OR(D85="",H85="",I85=""),0,IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D85="",H85="",I85=""),0,IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G85" s="7" t="n"/>
@@ -27115,7 +27431,7 @@
         <v/>
       </c>
       <c r="K85" s="9">
-        <f>IF(D85="","",IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D85="","",IFERROR(VLOOKUP(D85,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L85" s="9">
@@ -27129,11 +27445,11 @@
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="9">
-        <f>IF(D86="","",IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D86="","",IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F86" s="9">
-        <f>IF(OR(D86="",H86="",I86=""),0,IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D86="",H86="",I86=""),0,IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G86" s="7" t="n"/>
@@ -27144,7 +27460,7 @@
         <v/>
       </c>
       <c r="K86" s="9">
-        <f>IF(D86="","",IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D86="","",IFERROR(VLOOKUP(D86,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L86" s="9">
@@ -27158,11 +27474,11 @@
       <c r="C87" s="7" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="9">
-        <f>IF(D87="","",IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D87="","",IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F87" s="9">
-        <f>IF(OR(D87="",H87="",I87=""),0,IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D87="",H87="",I87=""),0,IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G87" s="7" t="n"/>
@@ -27173,7 +27489,7 @@
         <v/>
       </c>
       <c r="K87" s="9">
-        <f>IF(D87="","",IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D87="","",IFERROR(VLOOKUP(D87,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L87" s="9">
@@ -27187,11 +27503,11 @@
       <c r="C88" s="7" t="n"/>
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="9">
-        <f>IF(D88="","",IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D88="","",IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F88" s="9">
-        <f>IF(OR(D88="",H88="",I88=""),0,IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D88="",H88="",I88=""),0,IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G88" s="7" t="n"/>
@@ -27202,7 +27518,7 @@
         <v/>
       </c>
       <c r="K88" s="9">
-        <f>IF(D88="","",IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D88="","",IFERROR(VLOOKUP(D88,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L88" s="9">
@@ -27216,11 +27532,11 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="9">
-        <f>IF(D89="","",IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D89="","",IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>IF(OR(D89="",H89="",I89=""),0,IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D89="",H89="",I89=""),0,IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G89" s="7" t="n"/>
@@ -27231,7 +27547,7 @@
         <v/>
       </c>
       <c r="K89" s="9">
-        <f>IF(D89="","",IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D89="","",IFERROR(VLOOKUP(D89,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L89" s="9">
@@ -27245,11 +27561,11 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="9">
-        <f>IF(D90="","",IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D90="","",IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F90" s="9">
-        <f>IF(OR(D90="",H90="",I90=""),0,IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D90="",H90="",I90=""),0,IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G90" s="7" t="n"/>
@@ -27260,7 +27576,7 @@
         <v/>
       </c>
       <c r="K90" s="9">
-        <f>IF(D90="","",IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D90="","",IFERROR(VLOOKUP(D90,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L90" s="9">
@@ -27274,11 +27590,11 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="9">
-        <f>IF(D91="","",IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D91="","",IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F91" s="9">
-        <f>IF(OR(D91="",H91="",I91=""),0,IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D91="",H91="",I91=""),0,IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G91" s="7" t="n"/>
@@ -27289,7 +27605,7 @@
         <v/>
       </c>
       <c r="K91" s="9">
-        <f>IF(D91="","",IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D91="","",IFERROR(VLOOKUP(D91,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L91" s="9">
@@ -27303,11 +27619,11 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="9">
-        <f>IF(D92="","",IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D92="","",IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F92" s="9">
-        <f>IF(OR(D92="",H92="",I92=""),0,IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D92="",H92="",I92=""),0,IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G92" s="7" t="n"/>
@@ -27318,7 +27634,7 @@
         <v/>
       </c>
       <c r="K92" s="9">
-        <f>IF(D92="","",IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D92="","",IFERROR(VLOOKUP(D92,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L92" s="9">
@@ -27332,11 +27648,11 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="9">
-        <f>IF(D93="","",IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D93="","",IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F93" s="9">
-        <f>IF(OR(D93="",H93="",I93=""),0,IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D93="",H93="",I93=""),0,IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G93" s="7" t="n"/>
@@ -27347,7 +27663,7 @@
         <v/>
       </c>
       <c r="K93" s="9">
-        <f>IF(D93="","",IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D93="","",IFERROR(VLOOKUP(D93,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L93" s="9">
@@ -27361,11 +27677,11 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="9">
-        <f>IF(D94="","",IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D94="","",IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F94" s="9">
-        <f>IF(OR(D94="",H94="",I94=""),0,IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D94="",H94="",I94=""),0,IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G94" s="7" t="n"/>
@@ -27376,7 +27692,7 @@
         <v/>
       </c>
       <c r="K94" s="9">
-        <f>IF(D94="","",IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D94="","",IFERROR(VLOOKUP(D94,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L94" s="9">
@@ -27390,11 +27706,11 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="9">
-        <f>IF(D95="","",IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D95="","",IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F95" s="9">
-        <f>IF(OR(D95="",H95="",I95=""),0,IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D95="",H95="",I95=""),0,IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G95" s="7" t="n"/>
@@ -27405,7 +27721,7 @@
         <v/>
       </c>
       <c r="K95" s="9">
-        <f>IF(D95="","",IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D95="","",IFERROR(VLOOKUP(D95,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L95" s="9">
@@ -27419,11 +27735,11 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="9">
-        <f>IF(D96="","",IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D96="","",IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F96" s="9">
-        <f>IF(OR(D96="",H96="",I96=""),0,IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D96="",H96="",I96=""),0,IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G96" s="7" t="n"/>
@@ -27434,7 +27750,7 @@
         <v/>
       </c>
       <c r="K96" s="9">
-        <f>IF(D96="","",IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D96="","",IFERROR(VLOOKUP(D96,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L96" s="9">
@@ -27448,11 +27764,11 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="9">
-        <f>IF(D97="","",IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D97="","",IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F97" s="9">
-        <f>IF(OR(D97="",H97="",I97=""),0,IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D97="",H97="",I97=""),0,IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G97" s="7" t="n"/>
@@ -27463,7 +27779,7 @@
         <v/>
       </c>
       <c r="K97" s="9">
-        <f>IF(D97="","",IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D97="","",IFERROR(VLOOKUP(D97,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L97" s="9">
@@ -27477,11 +27793,11 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="9">
-        <f>IF(D98="","",IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D98="","",IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>IF(OR(D98="",H98="",I98=""),0,IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D98="",H98="",I98=""),0,IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -27492,7 +27808,7 @@
         <v/>
       </c>
       <c r="K98" s="9">
-        <f>IF(D98="","",IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D98="","",IFERROR(VLOOKUP(D98,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L98" s="9">
@@ -27506,11 +27822,11 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="9">
-        <f>IF(D99="","",IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D99="","",IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F99" s="9">
-        <f>IF(OR(D99="",H99="",I99=""),0,IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D99="",H99="",I99=""),0,IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G99" s="7" t="n"/>
@@ -27521,7 +27837,7 @@
         <v/>
       </c>
       <c r="K99" s="9">
-        <f>IF(D99="","",IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D99="","",IFERROR(VLOOKUP(D99,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L99" s="9">
@@ -27535,11 +27851,11 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="9">
-        <f>IF(D100="","",IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D100="","",IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F100" s="9">
-        <f>IF(OR(D100="",H100="",I100=""),0,IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D100="",H100="",I100=""),0,IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G100" s="7" t="n"/>
@@ -27550,7 +27866,7 @@
         <v/>
       </c>
       <c r="K100" s="9">
-        <f>IF(D100="","",IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D100="","",IFERROR(VLOOKUP(D100,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L100" s="9">
@@ -27564,11 +27880,11 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="9">
-        <f>IF(D101="","",IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D101="","",IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F101" s="9">
-        <f>IF(OR(D101="",H101="",I101=""),0,IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D101="",H101="",I101=""),0,IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G101" s="7" t="n"/>
@@ -27579,7 +27895,7 @@
         <v/>
       </c>
       <c r="K101" s="9">
-        <f>IF(D101="","",IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D101="","",IFERROR(VLOOKUP(D101,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L101" s="9">
@@ -27593,11 +27909,11 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="9">
-        <f>IF(D102="","",IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D102="","",IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F102" s="9">
-        <f>IF(OR(D102="",H102="",I102=""),0,IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D102="",H102="",I102=""),0,IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G102" s="7" t="n"/>
@@ -27608,7 +27924,7 @@
         <v/>
       </c>
       <c r="K102" s="9">
-        <f>IF(D102="","",IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D102="","",IFERROR(VLOOKUP(D102,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L102" s="9">
@@ -27622,11 +27938,11 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="9">
-        <f>IF(D103="","",IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D103="","",IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F103" s="9">
-        <f>IF(OR(D103="",H103="",I103=""),0,IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D103="",H103="",I103=""),0,IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G103" s="7" t="n"/>
@@ -27637,7 +27953,7 @@
         <v/>
       </c>
       <c r="K103" s="9">
-        <f>IF(D103="","",IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D103="","",IFERROR(VLOOKUP(D103,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L103" s="9">
@@ -27651,11 +27967,11 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="9">
-        <f>IF(D104="","",IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D104="","",IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F104" s="9">
-        <f>IF(OR(D104="",H104="",I104=""),0,IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D104="",H104="",I104=""),0,IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -27666,7 +27982,7 @@
         <v/>
       </c>
       <c r="K104" s="9">
-        <f>IF(D104="","",IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D104="","",IFERROR(VLOOKUP(D104,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L104" s="9">
@@ -27680,11 +27996,11 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="9">
-        <f>IF(D105="","",IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D105="","",IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F105" s="9">
-        <f>IF(OR(D105="",H105="",I105=""),0,IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D105="",H105="",I105=""),0,IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -27695,7 +28011,7 @@
         <v/>
       </c>
       <c r="K105" s="9">
-        <f>IF(D105="","",IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D105="","",IFERROR(VLOOKUP(D105,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L105" s="9">
@@ -27709,11 +28025,11 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="9">
-        <f>IF(D106="","",IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D106="","",IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F106" s="9">
-        <f>IF(OR(D106="",H106="",I106=""),0,IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D106="",H106="",I106=""),0,IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G106" s="7" t="n"/>
@@ -27724,7 +28040,7 @@
         <v/>
       </c>
       <c r="K106" s="9">
-        <f>IF(D106="","",IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D106="","",IFERROR(VLOOKUP(D106,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L106" s="9">
@@ -27738,11 +28054,11 @@
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="9">
-        <f>IF(D107="","",IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D107="","",IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F107" s="9">
-        <f>IF(OR(D107="",H107="",I107=""),0,IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D107="",H107="",I107=""),0,IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G107" s="7" t="n"/>
@@ -27753,7 +28069,7 @@
         <v/>
       </c>
       <c r="K107" s="9">
-        <f>IF(D107="","",IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D107="","",IFERROR(VLOOKUP(D107,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L107" s="9">
@@ -27767,11 +28083,11 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="9">
-        <f>IF(D108="","",IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D108="","",IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F108" s="9">
-        <f>IF(OR(D108="",H108="",I108=""),0,IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D108="",H108="",I108=""),0,IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G108" s="7" t="n"/>
@@ -27782,7 +28098,7 @@
         <v/>
       </c>
       <c r="K108" s="9">
-        <f>IF(D108="","",IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D108="","",IFERROR(VLOOKUP(D108,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L108" s="9">
@@ -27796,11 +28112,11 @@
       <c r="C109" s="7" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="9">
-        <f>IF(D109="","",IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D109="","",IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F109" s="9">
-        <f>IF(OR(D109="",H109="",I109=""),0,IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D109="",H109="",I109=""),0,IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -27811,7 +28127,7 @@
         <v/>
       </c>
       <c r="K109" s="9">
-        <f>IF(D109="","",IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D109="","",IFERROR(VLOOKUP(D109,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L109" s="9">
@@ -27825,11 +28141,11 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="9">
-        <f>IF(D110="","",IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D110="","",IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F110" s="9">
-        <f>IF(OR(D110="",H110="",I110=""),0,IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D110="",H110="",I110=""),0,IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G110" s="7" t="n"/>
@@ -27840,7 +28156,7 @@
         <v/>
       </c>
       <c r="K110" s="9">
-        <f>IF(D110="","",IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D110="","",IFERROR(VLOOKUP(D110,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L110" s="9">
@@ -27854,11 +28170,11 @@
       <c r="C111" s="7" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="9">
-        <f>IF(D111="","",IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D111="","",IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F111" s="9">
-        <f>IF(OR(D111="",H111="",I111=""),0,IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D111="",H111="",I111=""),0,IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -27869,7 +28185,7 @@
         <v/>
       </c>
       <c r="K111" s="9">
-        <f>IF(D111="","",IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D111="","",IFERROR(VLOOKUP(D111,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L111" s="9">
@@ -27883,11 +28199,11 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="9">
-        <f>IF(D112="","",IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D112="","",IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F112" s="9">
-        <f>IF(OR(D112="",H112="",I112=""),0,IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D112="",H112="",I112=""),0,IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -27898,7 +28214,7 @@
         <v/>
       </c>
       <c r="K112" s="9">
-        <f>IF(D112="","",IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D112="","",IFERROR(VLOOKUP(D112,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L112" s="9">
@@ -27912,11 +28228,11 @@
       <c r="C113" s="7" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="9">
-        <f>IF(D113="","",IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D113="","",IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F113" s="9">
-        <f>IF(OR(D113="",H113="",I113=""),0,IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D113="",H113="",I113=""),0,IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -27927,7 +28243,7 @@
         <v/>
       </c>
       <c r="K113" s="9">
-        <f>IF(D113="","",IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D113="","",IFERROR(VLOOKUP(D113,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L113" s="9">
@@ -27941,11 +28257,11 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="9">
-        <f>IF(D114="","",IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D114="","",IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F114" s="9">
-        <f>IF(OR(D114="",H114="",I114=""),0,IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D114="",H114="",I114=""),0,IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -27956,7 +28272,7 @@
         <v/>
       </c>
       <c r="K114" s="9">
-        <f>IF(D114="","",IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D114="","",IFERROR(VLOOKUP(D114,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L114" s="9">
@@ -27970,11 +28286,11 @@
       <c r="C115" s="7" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="9">
-        <f>IF(D115="","",IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D115="","",IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F115" s="9">
-        <f>IF(OR(D115="",H115="",I115=""),0,IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D115="",H115="",I115=""),0,IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -27985,7 +28301,7 @@
         <v/>
       </c>
       <c r="K115" s="9">
-        <f>IF(D115="","",IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D115="","",IFERROR(VLOOKUP(D115,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L115" s="9">
@@ -27999,11 +28315,11 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="9">
-        <f>IF(D116="","",IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D116="","",IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F116" s="9">
-        <f>IF(OR(D116="",H116="",I116=""),0,IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D116="",H116="",I116=""),0,IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -28014,7 +28330,7 @@
         <v/>
       </c>
       <c r="K116" s="9">
-        <f>IF(D116="","",IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D116="","",IFERROR(VLOOKUP(D116,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L116" s="9">
@@ -28028,11 +28344,11 @@
       <c r="C117" s="7" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="9">
-        <f>IF(D117="","",IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D117="","",IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F117" s="9">
-        <f>IF(OR(D117="",H117="",I117=""),0,IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D117="",H117="",I117=""),0,IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -28043,7 +28359,7 @@
         <v/>
       </c>
       <c r="K117" s="9">
-        <f>IF(D117="","",IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D117="","",IFERROR(VLOOKUP(D117,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L117" s="9">
@@ -28057,11 +28373,11 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="9">
-        <f>IF(D118="","",IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D118="","",IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F118" s="9">
-        <f>IF(OR(D118="",H118="",I118=""),0,IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D118="",H118="",I118=""),0,IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -28072,7 +28388,7 @@
         <v/>
       </c>
       <c r="K118" s="9">
-        <f>IF(D118="","",IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D118="","",IFERROR(VLOOKUP(D118,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L118" s="9">
@@ -28086,11 +28402,11 @@
       <c r="C119" s="7" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="9">
-        <f>IF(D119="","",IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D119="","",IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F119" s="9">
-        <f>IF(OR(D119="",H119="",I119=""),0,IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D119="",H119="",I119=""),0,IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G119" s="7" t="n"/>
@@ -28101,7 +28417,7 @@
         <v/>
       </c>
       <c r="K119" s="9">
-        <f>IF(D119="","",IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D119="","",IFERROR(VLOOKUP(D119,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L119" s="9">
@@ -28115,11 +28431,11 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="9">
-        <f>IF(D120="","",IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D120="","",IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F120" s="9">
-        <f>IF(OR(D120="",H120="",I120=""),0,IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D120="",H120="",I120=""),0,IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -28130,7 +28446,7 @@
         <v/>
       </c>
       <c r="K120" s="9">
-        <f>IF(D120="","",IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D120="","",IFERROR(VLOOKUP(D120,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L120" s="9">
@@ -28144,11 +28460,11 @@
       <c r="C121" s="7" t="n"/>
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="9">
-        <f>IF(D121="","",IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D121="","",IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F121" s="9">
-        <f>IF(OR(D121="",H121="",I121=""),0,IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D121="",H121="",I121=""),0,IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G121" s="7" t="n"/>
@@ -28159,7 +28475,7 @@
         <v/>
       </c>
       <c r="K121" s="9">
-        <f>IF(D121="","",IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D121="","",IFERROR(VLOOKUP(D121,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L121" s="9">
@@ -28173,11 +28489,11 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="9">
-        <f>IF(D122="","",IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D122="","",IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F122" s="9">
-        <f>IF(OR(D122="",H122="",I122=""),0,IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D122="",H122="",I122=""),0,IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -28188,7 +28504,7 @@
         <v/>
       </c>
       <c r="K122" s="9">
-        <f>IF(D122="","",IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D122="","",IFERROR(VLOOKUP(D122,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L122" s="9">
@@ -28202,11 +28518,11 @@
       <c r="C123" s="7" t="n"/>
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="9">
-        <f>IF(D123="","",IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D123="","",IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F123" s="9">
-        <f>IF(OR(D123="",H123="",I123=""),0,IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D123="",H123="",I123=""),0,IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G123" s="7" t="n"/>
@@ -28217,7 +28533,7 @@
         <v/>
       </c>
       <c r="K123" s="9">
-        <f>IF(D123="","",IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D123="","",IFERROR(VLOOKUP(D123,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L123" s="9">
@@ -28231,11 +28547,11 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="9">
-        <f>IF(D124="","",IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D124="","",IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F124" s="9">
-        <f>IF(OR(D124="",H124="",I124=""),0,IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D124="",H124="",I124=""),0,IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G124" s="7" t="n"/>
@@ -28246,7 +28562,7 @@
         <v/>
       </c>
       <c r="K124" s="9">
-        <f>IF(D124="","",IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D124="","",IFERROR(VLOOKUP(D124,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L124" s="9">
@@ -28260,11 +28576,11 @@
       <c r="C125" s="7" t="n"/>
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="9">
-        <f>IF(D125="","",IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D125="","",IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F125" s="9">
-        <f>IF(OR(D125="",H125="",I125=""),0,IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D125="",H125="",I125=""),0,IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G125" s="7" t="n"/>
@@ -28275,7 +28591,7 @@
         <v/>
       </c>
       <c r="K125" s="9">
-        <f>IF(D125="","",IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D125="","",IFERROR(VLOOKUP(D125,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L125" s="9">
@@ -28289,11 +28605,11 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="9">
-        <f>IF(D126="","",IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D126="","",IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F126" s="9">
-        <f>IF(OR(D126="",H126="",I126=""),0,IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D126="",H126="",I126=""),0,IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G126" s="7" t="n"/>
@@ -28304,7 +28620,7 @@
         <v/>
       </c>
       <c r="K126" s="9">
-        <f>IF(D126="","",IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D126="","",IFERROR(VLOOKUP(D126,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L126" s="9">
@@ -28318,11 +28634,11 @@
       <c r="C127" s="7" t="n"/>
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="9">
-        <f>IF(D127="","",IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D127="","",IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F127" s="9">
-        <f>IF(OR(D127="",H127="",I127=""),0,IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D127="",H127="",I127=""),0,IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G127" s="7" t="n"/>
@@ -28333,7 +28649,7 @@
         <v/>
       </c>
       <c r="K127" s="9">
-        <f>IF(D127="","",IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D127="","",IFERROR(VLOOKUP(D127,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L127" s="9">
@@ -28347,11 +28663,11 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="9">
-        <f>IF(D128="","",IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D128="","",IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F128" s="9">
-        <f>IF(OR(D128="",H128="",I128=""),0,IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D128="",H128="",I128=""),0,IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G128" s="7" t="n"/>
@@ -28362,7 +28678,7 @@
         <v/>
       </c>
       <c r="K128" s="9">
-        <f>IF(D128="","",IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D128="","",IFERROR(VLOOKUP(D128,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L128" s="9">
@@ -28376,11 +28692,11 @@
       <c r="C129" s="7" t="n"/>
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="9">
-        <f>IF(D129="","",IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D129="","",IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F129" s="9">
-        <f>IF(OR(D129="",H129="",I129=""),0,IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D129="",H129="",I129=""),0,IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G129" s="7" t="n"/>
@@ -28391,7 +28707,7 @@
         <v/>
       </c>
       <c r="K129" s="9">
-        <f>IF(D129="","",IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D129="","",IFERROR(VLOOKUP(D129,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L129" s="9">
@@ -28405,11 +28721,11 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="9">
-        <f>IF(D130="","",IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D130="","",IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F130" s="9">
-        <f>IF(OR(D130="",H130="",I130=""),0,IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D130="",H130="",I130=""),0,IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G130" s="7" t="n"/>
@@ -28420,7 +28736,7 @@
         <v/>
       </c>
       <c r="K130" s="9">
-        <f>IF(D130="","",IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D130="","",IFERROR(VLOOKUP(D130,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L130" s="9">
@@ -28434,11 +28750,11 @@
       <c r="C131" s="7" t="n"/>
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="9">
-        <f>IF(D131="","",IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D131="","",IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F131" s="9">
-        <f>IF(OR(D131="",H131="",I131=""),0,IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D131="",H131="",I131=""),0,IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G131" s="7" t="n"/>
@@ -28449,7 +28765,7 @@
         <v/>
       </c>
       <c r="K131" s="9">
-        <f>IF(D131="","",IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D131="","",IFERROR(VLOOKUP(D131,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L131" s="9">
@@ -28463,11 +28779,11 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="9">
-        <f>IF(D132="","",IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D132="","",IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F132" s="9">
-        <f>IF(OR(D132="",H132="",I132=""),0,IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D132="",H132="",I132=""),0,IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G132" s="7" t="n"/>
@@ -28478,7 +28794,7 @@
         <v/>
       </c>
       <c r="K132" s="9">
-        <f>IF(D132="","",IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D132="","",IFERROR(VLOOKUP(D132,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L132" s="9">
@@ -28492,11 +28808,11 @@
       <c r="C133" s="7" t="n"/>
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="9">
-        <f>IF(D133="","",IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D133="","",IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F133" s="9">
-        <f>IF(OR(D133="",H133="",I133=""),0,IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D133="",H133="",I133=""),0,IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G133" s="7" t="n"/>
@@ -28507,7 +28823,7 @@
         <v/>
       </c>
       <c r="K133" s="9">
-        <f>IF(D133="","",IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D133="","",IFERROR(VLOOKUP(D133,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L133" s="9">
@@ -28521,11 +28837,11 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="9">
-        <f>IF(D134="","",IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D134="","",IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F134" s="9">
-        <f>IF(OR(D134="",H134="",I134=""),0,IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D134="",H134="",I134=""),0,IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G134" s="7" t="n"/>
@@ -28536,7 +28852,7 @@
         <v/>
       </c>
       <c r="K134" s="9">
-        <f>IF(D134="","",IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D134="","",IFERROR(VLOOKUP(D134,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L134" s="9">
@@ -28550,11 +28866,11 @@
       <c r="C135" s="7" t="n"/>
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="9">
-        <f>IF(D135="","",IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D135="","",IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F135" s="9">
-        <f>IF(OR(D135="",H135="",I135=""),0,IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D135="",H135="",I135=""),0,IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G135" s="7" t="n"/>
@@ -28565,7 +28881,7 @@
         <v/>
       </c>
       <c r="K135" s="9">
-        <f>IF(D135="","",IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D135="","",IFERROR(VLOOKUP(D135,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L135" s="9">
@@ -28579,11 +28895,11 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="9">
-        <f>IF(D136="","",IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D136="","",IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F136" s="9">
-        <f>IF(OR(D136="",H136="",I136=""),0,IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D136="",H136="",I136=""),0,IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G136" s="7" t="n"/>
@@ -28594,7 +28910,7 @@
         <v/>
       </c>
       <c r="K136" s="9">
-        <f>IF(D136="","",IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D136="","",IFERROR(VLOOKUP(D136,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L136" s="9">
@@ -28608,11 +28924,11 @@
       <c r="C137" s="7" t="n"/>
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="9">
-        <f>IF(D137="","",IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D137="","",IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F137" s="9">
-        <f>IF(OR(D137="",H137="",I137=""),0,IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D137="",H137="",I137=""),0,IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G137" s="7" t="n"/>
@@ -28623,7 +28939,7 @@
         <v/>
       </c>
       <c r="K137" s="9">
-        <f>IF(D137="","",IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D137="","",IFERROR(VLOOKUP(D137,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L137" s="9">
@@ -28637,11 +28953,11 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="9">
-        <f>IF(D138="","",IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D138="","",IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F138" s="9">
-        <f>IF(OR(D138="",H138="",I138=""),0,IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D138="",H138="",I138=""),0,IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G138" s="7" t="n"/>
@@ -28652,7 +28968,7 @@
         <v/>
       </c>
       <c r="K138" s="9">
-        <f>IF(D138="","",IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D138="","",IFERROR(VLOOKUP(D138,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L138" s="9">
@@ -28666,11 +28982,11 @@
       <c r="C139" s="7" t="n"/>
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="9">
-        <f>IF(D139="","",IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D139="","",IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F139" s="9">
-        <f>IF(OR(D139="",H139="",I139=""),0,IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D139="",H139="",I139=""),0,IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G139" s="7" t="n"/>
@@ -28681,7 +28997,7 @@
         <v/>
       </c>
       <c r="K139" s="9">
-        <f>IF(D139="","",IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D139="","",IFERROR(VLOOKUP(D139,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L139" s="9">
@@ -28695,11 +29011,11 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="9">
-        <f>IF(D140="","",IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D140="","",IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F140" s="9">
-        <f>IF(OR(D140="",H140="",I140=""),0,IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D140="",H140="",I140=""),0,IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G140" s="7" t="n"/>
@@ -28710,7 +29026,7 @@
         <v/>
       </c>
       <c r="K140" s="9">
-        <f>IF(D140="","",IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D140="","",IFERROR(VLOOKUP(D140,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L140" s="9">
@@ -28724,11 +29040,11 @@
       <c r="C141" s="7" t="n"/>
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="9">
-        <f>IF(D141="","",IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D141="","",IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F141" s="9">
-        <f>IF(OR(D141="",H141="",I141=""),0,IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D141="",H141="",I141=""),0,IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G141" s="7" t="n"/>
@@ -28739,7 +29055,7 @@
         <v/>
       </c>
       <c r="K141" s="9">
-        <f>IF(D141="","",IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D141="","",IFERROR(VLOOKUP(D141,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L141" s="9">
@@ -28753,11 +29069,11 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="9">
-        <f>IF(D142="","",IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D142="","",IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F142" s="9">
-        <f>IF(OR(D142="",H142="",I142=""),0,IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D142="",H142="",I142=""),0,IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G142" s="7" t="n"/>
@@ -28768,7 +29084,7 @@
         <v/>
       </c>
       <c r="K142" s="9">
-        <f>IF(D142="","",IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D142="","",IFERROR(VLOOKUP(D142,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L142" s="9">
@@ -28782,11 +29098,11 @@
       <c r="C143" s="7" t="n"/>
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="9">
-        <f>IF(D143="","",IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D143="","",IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F143" s="9">
-        <f>IF(OR(D143="",H143="",I143=""),0,IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D143="",H143="",I143=""),0,IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G143" s="7" t="n"/>
@@ -28797,7 +29113,7 @@
         <v/>
       </c>
       <c r="K143" s="9">
-        <f>IF(D143="","",IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D143="","",IFERROR(VLOOKUP(D143,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L143" s="9">
@@ -28811,11 +29127,11 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="9">
-        <f>IF(D144="","",IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D144="","",IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F144" s="9">
-        <f>IF(OR(D144="",H144="",I144=""),0,IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D144="",H144="",I144=""),0,IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G144" s="7" t="n"/>
@@ -28826,7 +29142,7 @@
         <v/>
       </c>
       <c r="K144" s="9">
-        <f>IF(D144="","",IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D144="","",IFERROR(VLOOKUP(D144,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L144" s="9">
@@ -28840,11 +29156,11 @@
       <c r="C145" s="7" t="n"/>
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="9">
-        <f>IF(D145="","",IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D145="","",IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F145" s="9">
-        <f>IF(OR(D145="",H145="",I145=""),0,IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D145="",H145="",I145=""),0,IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G145" s="7" t="n"/>
@@ -28855,7 +29171,7 @@
         <v/>
       </c>
       <c r="K145" s="9">
-        <f>IF(D145="","",IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D145="","",IFERROR(VLOOKUP(D145,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L145" s="9">
@@ -28869,11 +29185,11 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="9">
-        <f>IF(D146="","",IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D146="","",IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F146" s="9">
-        <f>IF(OR(D146="",H146="",I146=""),0,IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D146="",H146="",I146=""),0,IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G146" s="7" t="n"/>
@@ -28884,7 +29200,7 @@
         <v/>
       </c>
       <c r="K146" s="9">
-        <f>IF(D146="","",IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D146="","",IFERROR(VLOOKUP(D146,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L146" s="9">
@@ -28898,11 +29214,11 @@
       <c r="C147" s="7" t="n"/>
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="9">
-        <f>IF(D147="","",IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D147="","",IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F147" s="9">
-        <f>IF(OR(D147="",H147="",I147=""),0,IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D147="",H147="",I147=""),0,IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G147" s="7" t="n"/>
@@ -28913,7 +29229,7 @@
         <v/>
       </c>
       <c r="K147" s="9">
-        <f>IF(D147="","",IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D147="","",IFERROR(VLOOKUP(D147,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L147" s="9">
@@ -28927,11 +29243,11 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="9">
-        <f>IF(D148="","",IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D148="","",IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F148" s="9">
-        <f>IF(OR(D148="",H148="",I148=""),0,IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D148="",H148="",I148=""),0,IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G148" s="7" t="n"/>
@@ -28942,7 +29258,7 @@
         <v/>
       </c>
       <c r="K148" s="9">
-        <f>IF(D148="","",IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D148="","",IFERROR(VLOOKUP(D148,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L148" s="9">
@@ -28956,11 +29272,11 @@
       <c r="C149" s="7" t="n"/>
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="9">
-        <f>IF(D149="","",IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D149="","",IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F149" s="9">
-        <f>IF(OR(D149="",H149="",I149=""),0,IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D149="",H149="",I149=""),0,IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G149" s="7" t="n"/>
@@ -28971,7 +29287,7 @@
         <v/>
       </c>
       <c r="K149" s="9">
-        <f>IF(D149="","",IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D149="","",IFERROR(VLOOKUP(D149,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L149" s="9">
@@ -28985,11 +29301,11 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="9">
-        <f>IF(D150="","",IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D150="","",IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F150" s="9">
-        <f>IF(OR(D150="",H150="",I150=""),0,IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D150="",H150="",I150=""),0,IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G150" s="7" t="n"/>
@@ -29000,7 +29316,7 @@
         <v/>
       </c>
       <c r="K150" s="9">
-        <f>IF(D150="","",IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D150="","",IFERROR(VLOOKUP(D150,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L150" s="9">
@@ -29014,11 +29330,11 @@
       <c r="C151" s="7" t="n"/>
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="9">
-        <f>IF(D151="","",IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D151="","",IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F151" s="9">
-        <f>IF(OR(D151="",H151="",I151=""),0,IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D151="",H151="",I151=""),0,IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G151" s="7" t="n"/>
@@ -29029,7 +29345,7 @@
         <v/>
       </c>
       <c r="K151" s="9">
-        <f>IF(D151="","",IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D151="","",IFERROR(VLOOKUP(D151,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L151" s="9">
@@ -29043,11 +29359,11 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="9">
-        <f>IF(D152="","",IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D152="","",IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F152" s="9">
-        <f>IF(OR(D152="",H152="",I152=""),0,IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D152="",H152="",I152=""),0,IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G152" s="7" t="n"/>
@@ -29058,7 +29374,7 @@
         <v/>
       </c>
       <c r="K152" s="9">
-        <f>IF(D152="","",IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D152="","",IFERROR(VLOOKUP(D152,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L152" s="9">
@@ -29072,11 +29388,11 @@
       <c r="C153" s="7" t="n"/>
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="9">
-        <f>IF(D153="","",IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D153="","",IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F153" s="9">
-        <f>IF(OR(D153="",H153="",I153=""),0,IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D153="",H153="",I153=""),0,IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G153" s="7" t="n"/>
@@ -29087,7 +29403,7 @@
         <v/>
       </c>
       <c r="K153" s="9">
-        <f>IF(D153="","",IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D153="","",IFERROR(VLOOKUP(D153,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L153" s="9">
@@ -29101,11 +29417,11 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="9">
-        <f>IF(D154="","",IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D154="","",IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F154" s="9">
-        <f>IF(OR(D154="",H154="",I154=""),0,IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D154="",H154="",I154=""),0,IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G154" s="7" t="n"/>
@@ -29116,7 +29432,7 @@
         <v/>
       </c>
       <c r="K154" s="9">
-        <f>IF(D154="","",IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D154="","",IFERROR(VLOOKUP(D154,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L154" s="9">
@@ -29130,11 +29446,11 @@
       <c r="C155" s="7" t="n"/>
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="9">
-        <f>IF(D155="","",IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D155="","",IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F155" s="9">
-        <f>IF(OR(D155="",H155="",I155=""),0,IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D155="",H155="",I155=""),0,IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G155" s="7" t="n"/>
@@ -29145,7 +29461,7 @@
         <v/>
       </c>
       <c r="K155" s="9">
-        <f>IF(D155="","",IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D155="","",IFERROR(VLOOKUP(D155,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L155" s="9">
@@ -29159,11 +29475,11 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="9">
-        <f>IF(D156="","",IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D156="","",IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F156" s="9">
-        <f>IF(OR(D156="",H156="",I156=""),0,IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D156="",H156="",I156=""),0,IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G156" s="7" t="n"/>
@@ -29174,7 +29490,7 @@
         <v/>
       </c>
       <c r="K156" s="9">
-        <f>IF(D156="","",IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D156="","",IFERROR(VLOOKUP(D156,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L156" s="9">
@@ -29188,11 +29504,11 @@
       <c r="C157" s="7" t="n"/>
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="9">
-        <f>IF(D157="","",IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D157="","",IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F157" s="9">
-        <f>IF(OR(D157="",H157="",I157=""),0,IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D157="",H157="",I157=""),0,IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G157" s="7" t="n"/>
@@ -29203,7 +29519,7 @@
         <v/>
       </c>
       <c r="K157" s="9">
-        <f>IF(D157="","",IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D157="","",IFERROR(VLOOKUP(D157,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L157" s="9">
@@ -29217,11 +29533,11 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="9">
-        <f>IF(D158="","",IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D158="","",IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F158" s="9">
-        <f>IF(OR(D158="",H158="",I158=""),0,IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D158="",H158="",I158=""),0,IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G158" s="7" t="n"/>
@@ -29232,7 +29548,7 @@
         <v/>
       </c>
       <c r="K158" s="9">
-        <f>IF(D158="","",IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D158="","",IFERROR(VLOOKUP(D158,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L158" s="9">
@@ -29246,11 +29562,11 @@
       <c r="C159" s="7" t="n"/>
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="9">
-        <f>IF(D159="","",IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D159="","",IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F159" s="9">
-        <f>IF(OR(D159="",H159="",I159=""),0,IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D159="",H159="",I159=""),0,IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G159" s="7" t="n"/>
@@ -29261,7 +29577,7 @@
         <v/>
       </c>
       <c r="K159" s="9">
-        <f>IF(D159="","",IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D159="","",IFERROR(VLOOKUP(D159,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L159" s="9">
@@ -29275,11 +29591,11 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="9">
-        <f>IF(D160="","",IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D160="","",IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F160" s="9">
-        <f>IF(OR(D160="",H160="",I160=""),0,IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D160="",H160="",I160=""),0,IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G160" s="7" t="n"/>
@@ -29290,7 +29606,7 @@
         <v/>
       </c>
       <c r="K160" s="9">
-        <f>IF(D160="","",IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D160="","",IFERROR(VLOOKUP(D160,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L160" s="9">
@@ -29304,11 +29620,11 @@
       <c r="C161" s="7" t="n"/>
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="9">
-        <f>IF(D161="","",IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D161="","",IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F161" s="9">
-        <f>IF(OR(D161="",H161="",I161=""),0,IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D161="",H161="",I161=""),0,IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G161" s="7" t="n"/>
@@ -29319,7 +29635,7 @@
         <v/>
       </c>
       <c r="K161" s="9">
-        <f>IF(D161="","",IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D161="","",IFERROR(VLOOKUP(D161,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L161" s="9">
@@ -29333,11 +29649,11 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="9">
-        <f>IF(D162="","",IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D162="","",IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F162" s="9">
-        <f>IF(OR(D162="",H162="",I162=""),0,IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D162="",H162="",I162=""),0,IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G162" s="7" t="n"/>
@@ -29348,7 +29664,7 @@
         <v/>
       </c>
       <c r="K162" s="9">
-        <f>IF(D162="","",IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D162="","",IFERROR(VLOOKUP(D162,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L162" s="9">
@@ -29362,11 +29678,11 @@
       <c r="C163" s="7" t="n"/>
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="9">
-        <f>IF(D163="","",IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D163="","",IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F163" s="9">
-        <f>IF(OR(D163="",H163="",I163=""),0,IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D163="",H163="",I163=""),0,IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G163" s="7" t="n"/>
@@ -29377,7 +29693,7 @@
         <v/>
       </c>
       <c r="K163" s="9">
-        <f>IF(D163="","",IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D163="","",IFERROR(VLOOKUP(D163,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L163" s="9">
@@ -29391,11 +29707,11 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="9">
-        <f>IF(D164="","",IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D164="","",IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F164" s="9">
-        <f>IF(OR(D164="",H164="",I164=""),0,IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D164="",H164="",I164=""),0,IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G164" s="7" t="n"/>
@@ -29406,7 +29722,7 @@
         <v/>
       </c>
       <c r="K164" s="9">
-        <f>IF(D164="","",IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D164="","",IFERROR(VLOOKUP(D164,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L164" s="9">
@@ -29420,11 +29736,11 @@
       <c r="C165" s="7" t="n"/>
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="9">
-        <f>IF(D165="","",IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D165="","",IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F165" s="9">
-        <f>IF(OR(D165="",H165="",I165=""),0,IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D165="",H165="",I165=""),0,IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G165" s="7" t="n"/>
@@ -29435,7 +29751,7 @@
         <v/>
       </c>
       <c r="K165" s="9">
-        <f>IF(D165="","",IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D165="","",IFERROR(VLOOKUP(D165,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L165" s="9">
@@ -29449,11 +29765,11 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="9">
-        <f>IF(D166="","",IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D166="","",IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F166" s="9">
-        <f>IF(OR(D166="",H166="",I166=""),0,IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D166="",H166="",I166=""),0,IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G166" s="7" t="n"/>
@@ -29464,7 +29780,7 @@
         <v/>
       </c>
       <c r="K166" s="9">
-        <f>IF(D166="","",IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D166="","",IFERROR(VLOOKUP(D166,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L166" s="9">
@@ -29478,11 +29794,11 @@
       <c r="C167" s="7" t="n"/>
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="9">
-        <f>IF(D167="","",IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D167="","",IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F167" s="9">
-        <f>IF(OR(D167="",H167="",I167=""),0,IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D167="",H167="",I167=""),0,IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G167" s="7" t="n"/>
@@ -29493,7 +29809,7 @@
         <v/>
       </c>
       <c r="K167" s="9">
-        <f>IF(D167="","",IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D167="","",IFERROR(VLOOKUP(D167,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L167" s="9">
@@ -29507,11 +29823,11 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="9">
-        <f>IF(D168="","",IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D168="","",IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F168" s="9">
-        <f>IF(OR(D168="",H168="",I168=""),0,IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D168="",H168="",I168=""),0,IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G168" s="7" t="n"/>
@@ -29522,7 +29838,7 @@
         <v/>
       </c>
       <c r="K168" s="9">
-        <f>IF(D168="","",IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D168="","",IFERROR(VLOOKUP(D168,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L168" s="9">
@@ -29536,11 +29852,11 @@
       <c r="C169" s="7" t="n"/>
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="9">
-        <f>IF(D169="","",IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D169="","",IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F169" s="9">
-        <f>IF(OR(D169="",H169="",I169=""),0,IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D169="",H169="",I169=""),0,IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G169" s="7" t="n"/>
@@ -29551,7 +29867,7 @@
         <v/>
       </c>
       <c r="K169" s="9">
-        <f>IF(D169="","",IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D169="","",IFERROR(VLOOKUP(D169,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L169" s="9">
@@ -29565,11 +29881,11 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="9">
-        <f>IF(D170="","",IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D170="","",IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F170" s="9">
-        <f>IF(OR(D170="",H170="",I170=""),0,IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D170="",H170="",I170=""),0,IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G170" s="7" t="n"/>
@@ -29580,7 +29896,7 @@
         <v/>
       </c>
       <c r="K170" s="9">
-        <f>IF(D170="","",IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D170="","",IFERROR(VLOOKUP(D170,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L170" s="9">
@@ -29594,11 +29910,11 @@
       <c r="C171" s="7" t="n"/>
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="9">
-        <f>IF(D171="","",IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D171="","",IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F171" s="9">
-        <f>IF(OR(D171="",H171="",I171=""),0,IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D171="",H171="",I171=""),0,IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G171" s="7" t="n"/>
@@ -29609,7 +29925,7 @@
         <v/>
       </c>
       <c r="K171" s="9">
-        <f>IF(D171="","",IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D171="","",IFERROR(VLOOKUP(D171,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L171" s="9">
@@ -29623,11 +29939,11 @@
       <c r="C172" s="7" t="n"/>
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="9">
-        <f>IF(D172="","",IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D172="","",IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F172" s="9">
-        <f>IF(OR(D172="",H172="",I172=""),0,IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D172="",H172="",I172=""),0,IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G172" s="7" t="n"/>
@@ -29638,7 +29954,7 @@
         <v/>
       </c>
       <c r="K172" s="9">
-        <f>IF(D172="","",IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D172="","",IFERROR(VLOOKUP(D172,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L172" s="9">
@@ -29652,11 +29968,11 @@
       <c r="C173" s="7" t="n"/>
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="9">
-        <f>IF(D173="","",IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D173="","",IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F173" s="9">
-        <f>IF(OR(D173="",H173="",I173=""),0,IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D173="",H173="",I173=""),0,IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G173" s="7" t="n"/>
@@ -29667,7 +29983,7 @@
         <v/>
       </c>
       <c r="K173" s="9">
-        <f>IF(D173="","",IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D173="","",IFERROR(VLOOKUP(D173,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L173" s="9">
@@ -29681,11 +29997,11 @@
       <c r="C174" s="7" t="n"/>
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="9">
-        <f>IF(D174="","",IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D174="","",IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F174" s="9">
-        <f>IF(OR(D174="",H174="",I174=""),0,IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D174="",H174="",I174=""),0,IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G174" s="7" t="n"/>
@@ -29696,7 +30012,7 @@
         <v/>
       </c>
       <c r="K174" s="9">
-        <f>IF(D174="","",IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D174="","",IFERROR(VLOOKUP(D174,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L174" s="9">
@@ -29710,11 +30026,11 @@
       <c r="C175" s="7" t="n"/>
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="9">
-        <f>IF(D175="","",IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D175="","",IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F175" s="9">
-        <f>IF(OR(D175="",H175="",I175=""),0,IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D175="",H175="",I175=""),0,IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G175" s="7" t="n"/>
@@ -29725,7 +30041,7 @@
         <v/>
       </c>
       <c r="K175" s="9">
-        <f>IF(D175="","",IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D175="","",IFERROR(VLOOKUP(D175,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L175" s="9">
@@ -29739,11 +30055,11 @@
       <c r="C176" s="7" t="n"/>
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="9">
-        <f>IF(D176="","",IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D176="","",IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F176" s="9">
-        <f>IF(OR(D176="",H176="",I176=""),0,IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D176="",H176="",I176=""),0,IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G176" s="7" t="n"/>
@@ -29754,7 +30070,7 @@
         <v/>
       </c>
       <c r="K176" s="9">
-        <f>IF(D176="","",IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D176="","",IFERROR(VLOOKUP(D176,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L176" s="9">
@@ -29768,11 +30084,11 @@
       <c r="C177" s="7" t="n"/>
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="9">
-        <f>IF(D177="","",IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D177="","",IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F177" s="9">
-        <f>IF(OR(D177="",H177="",I177=""),0,IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D177="",H177="",I177=""),0,IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G177" s="7" t="n"/>
@@ -29783,7 +30099,7 @@
         <v/>
       </c>
       <c r="K177" s="9">
-        <f>IF(D177="","",IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D177="","",IFERROR(VLOOKUP(D177,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L177" s="9">
@@ -29797,11 +30113,11 @@
       <c r="C178" s="7" t="n"/>
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="9">
-        <f>IF(D178="","",IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D178="","",IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F178" s="9">
-        <f>IF(OR(D178="",H178="",I178=""),0,IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D178="",H178="",I178=""),0,IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G178" s="7" t="n"/>
@@ -29812,7 +30128,7 @@
         <v/>
       </c>
       <c r="K178" s="9">
-        <f>IF(D178="","",IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D178="","",IFERROR(VLOOKUP(D178,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L178" s="9">
@@ -29826,11 +30142,11 @@
       <c r="C179" s="7" t="n"/>
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="9">
-        <f>IF(D179="","",IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D179="","",IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F179" s="9">
-        <f>IF(OR(D179="",H179="",I179=""),0,IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D179="",H179="",I179=""),0,IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G179" s="7" t="n"/>
@@ -29841,7 +30157,7 @@
         <v/>
       </c>
       <c r="K179" s="9">
-        <f>IF(D179="","",IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D179="","",IFERROR(VLOOKUP(D179,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L179" s="9">
@@ -29855,11 +30171,11 @@
       <c r="C180" s="7" t="n"/>
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="9">
-        <f>IF(D180="","",IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D180="","",IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F180" s="9">
-        <f>IF(OR(D180="",H180="",I180=""),0,IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D180="",H180="",I180=""),0,IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G180" s="7" t="n"/>
@@ -29870,7 +30186,7 @@
         <v/>
       </c>
       <c r="K180" s="9">
-        <f>IF(D180="","",IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D180="","",IFERROR(VLOOKUP(D180,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L180" s="9">
@@ -29884,11 +30200,11 @@
       <c r="C181" s="7" t="n"/>
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="9">
-        <f>IF(D181="","",IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D181="","",IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F181" s="9">
-        <f>IF(OR(D181="",H181="",I181=""),0,IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D181="",H181="",I181=""),0,IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G181" s="7" t="n"/>
@@ -29899,7 +30215,7 @@
         <v/>
       </c>
       <c r="K181" s="9">
-        <f>IF(D181="","",IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D181="","",IFERROR(VLOOKUP(D181,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L181" s="9">
@@ -29913,11 +30229,11 @@
       <c r="C182" s="7" t="n"/>
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="9">
-        <f>IF(D182="","",IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D182="","",IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F182" s="9">
-        <f>IF(OR(D182="",H182="",I182=""),0,IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D182="",H182="",I182=""),0,IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G182" s="7" t="n"/>
@@ -29928,7 +30244,7 @@
         <v/>
       </c>
       <c r="K182" s="9">
-        <f>IF(D182="","",IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D182="","",IFERROR(VLOOKUP(D182,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L182" s="9">
@@ -29942,11 +30258,11 @@
       <c r="C183" s="7" t="n"/>
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="9">
-        <f>IF(D183="","",IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D183="","",IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F183" s="9">
-        <f>IF(OR(D183="",H183="",I183=""),0,IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D183="",H183="",I183=""),0,IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G183" s="7" t="n"/>
@@ -29957,7 +30273,7 @@
         <v/>
       </c>
       <c r="K183" s="9">
-        <f>IF(D183="","",IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D183="","",IFERROR(VLOOKUP(D183,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L183" s="9">
@@ -29971,11 +30287,11 @@
       <c r="C184" s="7" t="n"/>
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="9">
-        <f>IF(D184="","",IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D184="","",IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F184" s="9">
-        <f>IF(OR(D184="",H184="",I184=""),0,IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D184="",H184="",I184=""),0,IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G184" s="7" t="n"/>
@@ -29986,7 +30302,7 @@
         <v/>
       </c>
       <c r="K184" s="9">
-        <f>IF(D184="","",IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D184="","",IFERROR(VLOOKUP(D184,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L184" s="9">
@@ -30000,11 +30316,11 @@
       <c r="C185" s="7" t="n"/>
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="9">
-        <f>IF(D185="","",IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D185="","",IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F185" s="9">
-        <f>IF(OR(D185="",H185="",I185=""),0,IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D185="",H185="",I185=""),0,IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G185" s="7" t="n"/>
@@ -30015,7 +30331,7 @@
         <v/>
       </c>
       <c r="K185" s="9">
-        <f>IF(D185="","",IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D185="","",IFERROR(VLOOKUP(D185,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L185" s="9">
@@ -30029,11 +30345,11 @@
       <c r="C186" s="7" t="n"/>
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="9">
-        <f>IF(D186="","",IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D186="","",IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F186" s="9">
-        <f>IF(OR(D186="",H186="",I186=""),0,IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D186="",H186="",I186=""),0,IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G186" s="7" t="n"/>
@@ -30044,7 +30360,7 @@
         <v/>
       </c>
       <c r="K186" s="9">
-        <f>IF(D186="","",IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D186="","",IFERROR(VLOOKUP(D186,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L186" s="9">
@@ -30058,11 +30374,11 @@
       <c r="C187" s="7" t="n"/>
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="9">
-        <f>IF(D187="","",IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D187="","",IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F187" s="9">
-        <f>IF(OR(D187="",H187="",I187=""),0,IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D187="",H187="",I187=""),0,IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G187" s="7" t="n"/>
@@ -30073,7 +30389,7 @@
         <v/>
       </c>
       <c r="K187" s="9">
-        <f>IF(D187="","",IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D187="","",IFERROR(VLOOKUP(D187,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L187" s="9">
@@ -30087,11 +30403,11 @@
       <c r="C188" s="7" t="n"/>
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="9">
-        <f>IF(D188="","",IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D188="","",IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F188" s="9">
-        <f>IF(OR(D188="",H188="",I188=""),0,IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D188="",H188="",I188=""),0,IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G188" s="7" t="n"/>
@@ -30102,7 +30418,7 @@
         <v/>
       </c>
       <c r="K188" s="9">
-        <f>IF(D188="","",IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D188="","",IFERROR(VLOOKUP(D188,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L188" s="9">
@@ -30116,11 +30432,11 @@
       <c r="C189" s="7" t="n"/>
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="9">
-        <f>IF(D189="","",IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D189="","",IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F189" s="9">
-        <f>IF(OR(D189="",H189="",I189=""),0,IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D189="",H189="",I189=""),0,IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G189" s="7" t="n"/>
@@ -30131,7 +30447,7 @@
         <v/>
       </c>
       <c r="K189" s="9">
-        <f>IF(D189="","",IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D189="","",IFERROR(VLOOKUP(D189,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L189" s="9">
@@ -30145,11 +30461,11 @@
       <c r="C190" s="7" t="n"/>
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="9">
-        <f>IF(D190="","",IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D190="","",IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F190" s="9">
-        <f>IF(OR(D190="",H190="",I190=""),0,IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D190="",H190="",I190=""),0,IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G190" s="7" t="n"/>
@@ -30160,7 +30476,7 @@
         <v/>
       </c>
       <c r="K190" s="9">
-        <f>IF(D190="","",IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D190="","",IFERROR(VLOOKUP(D190,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L190" s="9">
@@ -30174,11 +30490,11 @@
       <c r="C191" s="7" t="n"/>
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="9">
-        <f>IF(D191="","",IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D191="","",IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F191" s="9">
-        <f>IF(OR(D191="",H191="",I191=""),0,IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D191="",H191="",I191=""),0,IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G191" s="7" t="n"/>
@@ -30189,7 +30505,7 @@
         <v/>
       </c>
       <c r="K191" s="9">
-        <f>IF(D191="","",IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D191="","",IFERROR(VLOOKUP(D191,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L191" s="9">
@@ -30203,11 +30519,11 @@
       <c r="C192" s="7" t="n"/>
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="9">
-        <f>IF(D192="","",IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D192="","",IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F192" s="9">
-        <f>IF(OR(D192="",H192="",I192=""),0,IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D192="",H192="",I192=""),0,IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G192" s="7" t="n"/>
@@ -30218,7 +30534,7 @@
         <v/>
       </c>
       <c r="K192" s="9">
-        <f>IF(D192="","",IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D192="","",IFERROR(VLOOKUP(D192,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L192" s="9">
@@ -30232,11 +30548,11 @@
       <c r="C193" s="7" t="n"/>
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="9">
-        <f>IF(D193="","",IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D193="","",IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F193" s="9">
-        <f>IF(OR(D193="",H193="",I193=""),0,IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D193="",H193="",I193=""),0,IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G193" s="7" t="n"/>
@@ -30247,7 +30563,7 @@
         <v/>
       </c>
       <c r="K193" s="9">
-        <f>IF(D193="","",IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D193="","",IFERROR(VLOOKUP(D193,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L193" s="9">
@@ -30261,11 +30577,11 @@
       <c r="C194" s="7" t="n"/>
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="9">
-        <f>IF(D194="","",IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D194="","",IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F194" s="9">
-        <f>IF(OR(D194="",H194="",I194=""),0,IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D194="",H194="",I194=""),0,IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G194" s="7" t="n"/>
@@ -30276,7 +30592,7 @@
         <v/>
       </c>
       <c r="K194" s="9">
-        <f>IF(D194="","",IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D194="","",IFERROR(VLOOKUP(D194,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L194" s="9">
@@ -30290,11 +30606,11 @@
       <c r="C195" s="7" t="n"/>
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="9">
-        <f>IF(D195="","",IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D195="","",IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F195" s="9">
-        <f>IF(OR(D195="",H195="",I195=""),0,IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D195="",H195="",I195=""),0,IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G195" s="7" t="n"/>
@@ -30305,7 +30621,7 @@
         <v/>
       </c>
       <c r="K195" s="9">
-        <f>IF(D195="","",IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D195="","",IFERROR(VLOOKUP(D195,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L195" s="9">
@@ -30319,11 +30635,11 @@
       <c r="C196" s="7" t="n"/>
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="9">
-        <f>IF(D196="","",IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D196="","",IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F196" s="9">
-        <f>IF(OR(D196="",H196="",I196=""),0,IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D196="",H196="",I196=""),0,IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G196" s="7" t="n"/>
@@ -30334,7 +30650,7 @@
         <v/>
       </c>
       <c r="K196" s="9">
-        <f>IF(D196="","",IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D196="","",IFERROR(VLOOKUP(D196,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L196" s="9">
@@ -30348,11 +30664,11 @@
       <c r="C197" s="7" t="n"/>
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="9">
-        <f>IF(D197="","",IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D197="","",IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F197" s="9">
-        <f>IF(OR(D197="",H197="",I197=""),0,IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D197="",H197="",I197=""),0,IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G197" s="7" t="n"/>
@@ -30363,7 +30679,7 @@
         <v/>
       </c>
       <c r="K197" s="9">
-        <f>IF(D197="","",IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D197="","",IFERROR(VLOOKUP(D197,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L197" s="9">
@@ -30377,11 +30693,11 @@
       <c r="C198" s="7" t="n"/>
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="9">
-        <f>IF(D198="","",IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D198="","",IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F198" s="9">
-        <f>IF(OR(D198="",H198="",I198=""),0,IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D198="",H198="",I198=""),0,IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G198" s="7" t="n"/>
@@ -30392,7 +30708,7 @@
         <v/>
       </c>
       <c r="K198" s="9">
-        <f>IF(D198="","",IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D198="","",IFERROR(VLOOKUP(D198,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L198" s="9">
@@ -30406,11 +30722,11 @@
       <c r="C199" s="7" t="n"/>
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="9">
-        <f>IF(D199="","",IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D199="","",IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F199" s="9">
-        <f>IF(OR(D199="",H199="",I199=""),0,IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D199="",H199="",I199=""),0,IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G199" s="7" t="n"/>
@@ -30421,7 +30737,7 @@
         <v/>
       </c>
       <c r="K199" s="9">
-        <f>IF(D199="","",IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D199="","",IFERROR(VLOOKUP(D199,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L199" s="9">
@@ -30435,11 +30751,11 @@
       <c r="C200" s="7" t="n"/>
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="9">
-        <f>IF(D200="","",IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D200="","",IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F200" s="9">
-        <f>IF(OR(D200="",H200="",I200=""),0,IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D200="",H200="",I200=""),0,IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G200" s="7" t="n"/>
@@ -30450,7 +30766,7 @@
         <v/>
       </c>
       <c r="K200" s="9">
-        <f>IF(D200="","",IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D200="","",IFERROR(VLOOKUP(D200,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L200" s="9">
@@ -30464,11 +30780,11 @@
       <c r="C201" s="7" t="n"/>
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="9">
-        <f>IF(D201="","",IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D201="","",IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F201" s="9">
-        <f>IF(OR(D201="",H201="",I201=""),0,IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D201="",H201="",I201=""),0,IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G201" s="7" t="n"/>
@@ -30479,7 +30795,7 @@
         <v/>
       </c>
       <c r="K201" s="9">
-        <f>IF(D201="","",IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D201="","",IFERROR(VLOOKUP(D201,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L201" s="9">
@@ -30493,11 +30809,11 @@
       <c r="C202" s="7" t="n"/>
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="9">
-        <f>IF(D202="","",IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D202="","",IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F202" s="9">
-        <f>IF(OR(D202="",H202="",I202=""),0,IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D202="",H202="",I202=""),0,IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G202" s="7" t="n"/>
@@ -30508,7 +30824,7 @@
         <v/>
       </c>
       <c r="K202" s="9">
-        <f>IF(D202="","",IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D202="","",IFERROR(VLOOKUP(D202,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L202" s="9">
@@ -30522,11 +30838,11 @@
       <c r="C203" s="7" t="n"/>
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="9">
-        <f>IF(D203="","",IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D203="","",IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F203" s="9">
-        <f>IF(OR(D203="",H203="",I203=""),0,IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D203="",H203="",I203=""),0,IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G203" s="7" t="n"/>
@@ -30537,7 +30853,7 @@
         <v/>
       </c>
       <c r="K203" s="9">
-        <f>IF(D203="","",IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D203="","",IFERROR(VLOOKUP(D203,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L203" s="9">
@@ -30551,11 +30867,11 @@
       <c r="C204" s="7" t="n"/>
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="9">
-        <f>IF(D204="","",IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D204="","",IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F204" s="9">
-        <f>IF(OR(D204="",H204="",I204=""),0,IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D204="",H204="",I204=""),0,IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G204" s="7" t="n"/>
@@ -30566,7 +30882,7 @@
         <v/>
       </c>
       <c r="K204" s="9">
-        <f>IF(D204="","",IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D204="","",IFERROR(VLOOKUP(D204,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L204" s="9">
@@ -30580,11 +30896,11 @@
       <c r="C205" s="7" t="n"/>
       <c r="D205" s="7" t="n"/>
       <c r="E205" s="9">
-        <f>IF(D205="","",IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D205="","",IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F205" s="9">
-        <f>IF(OR(D205="",H205="",I205=""),0,IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D205="",H205="",I205=""),0,IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G205" s="7" t="n"/>
@@ -30595,7 +30911,7 @@
         <v/>
       </c>
       <c r="K205" s="9">
-        <f>IF(D205="","",IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D205="","",IFERROR(VLOOKUP(D205,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L205" s="9">
@@ -30609,11 +30925,11 @@
       <c r="C206" s="7" t="n"/>
       <c r="D206" s="7" t="n"/>
       <c r="E206" s="9">
-        <f>IF(D206="","",IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D206="","",IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F206" s="9">
-        <f>IF(OR(D206="",H206="",I206=""),0,IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D206="",H206="",I206=""),0,IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G206" s="7" t="n"/>
@@ -30624,7 +30940,7 @@
         <v/>
       </c>
       <c r="K206" s="9">
-        <f>IF(D206="","",IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D206="","",IFERROR(VLOOKUP(D206,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L206" s="9">
@@ -30638,11 +30954,11 @@
       <c r="C207" s="7" t="n"/>
       <c r="D207" s="7" t="n"/>
       <c r="E207" s="9">
-        <f>IF(D207="","",IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D207="","",IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F207" s="9">
-        <f>IF(OR(D207="",H207="",I207=""),0,IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D207="",H207="",I207=""),0,IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G207" s="7" t="n"/>
@@ -30653,7 +30969,7 @@
         <v/>
       </c>
       <c r="K207" s="9">
-        <f>IF(D207="","",IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D207="","",IFERROR(VLOOKUP(D207,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L207" s="9">
@@ -30667,11 +30983,11 @@
       <c r="C208" s="7" t="n"/>
       <c r="D208" s="7" t="n"/>
       <c r="E208" s="9">
-        <f>IF(D208="","",IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D208="","",IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F208" s="9">
-        <f>IF(OR(D208="",H208="",I208=""),0,IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D208="",H208="",I208=""),0,IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G208" s="7" t="n"/>
@@ -30682,7 +30998,7 @@
         <v/>
       </c>
       <c r="K208" s="9">
-        <f>IF(D208="","",IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D208="","",IFERROR(VLOOKUP(D208,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L208" s="9">
@@ -30696,11 +31012,11 @@
       <c r="C209" s="7" t="n"/>
       <c r="D209" s="7" t="n"/>
       <c r="E209" s="9">
-        <f>IF(D209="","",IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D209="","",IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F209" s="9">
-        <f>IF(OR(D209="",H209="",I209=""),0,IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D209="",H209="",I209=""),0,IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G209" s="7" t="n"/>
@@ -30711,7 +31027,7 @@
         <v/>
       </c>
       <c r="K209" s="9">
-        <f>IF(D209="","",IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D209="","",IFERROR(VLOOKUP(D209,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L209" s="9">
@@ -30725,11 +31041,11 @@
       <c r="C210" s="7" t="n"/>
       <c r="D210" s="7" t="n"/>
       <c r="E210" s="9">
-        <f>IF(D210="","",IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D210="","",IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F210" s="9">
-        <f>IF(OR(D210="",H210="",I210=""),0,IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D210="",H210="",I210=""),0,IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G210" s="7" t="n"/>
@@ -30740,7 +31056,7 @@
         <v/>
       </c>
       <c r="K210" s="9">
-        <f>IF(D210="","",IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D210="","",IFERROR(VLOOKUP(D210,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L210" s="9">
@@ -30754,11 +31070,11 @@
       <c r="C211" s="7" t="n"/>
       <c r="D211" s="7" t="n"/>
       <c r="E211" s="9">
-        <f>IF(D211="","",IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D211="","",IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F211" s="9">
-        <f>IF(OR(D211="",H211="",I211=""),0,IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D211="",H211="",I211=""),0,IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G211" s="7" t="n"/>
@@ -30769,7 +31085,7 @@
         <v/>
       </c>
       <c r="K211" s="9">
-        <f>IF(D211="","",IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D211="","",IFERROR(VLOOKUP(D211,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L211" s="9">
@@ -30783,11 +31099,11 @@
       <c r="C212" s="7" t="n"/>
       <c r="D212" s="7" t="n"/>
       <c r="E212" s="9">
-        <f>IF(D212="","",IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D212="","",IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F212" s="9">
-        <f>IF(OR(D212="",H212="",I212=""),0,IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D212="",H212="",I212=""),0,IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G212" s="7" t="n"/>
@@ -30798,7 +31114,7 @@
         <v/>
       </c>
       <c r="K212" s="9">
-        <f>IF(D212="","",IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D212="","",IFERROR(VLOOKUP(D212,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L212" s="9">
@@ -30812,11 +31128,11 @@
       <c r="C213" s="7" t="n"/>
       <c r="D213" s="7" t="n"/>
       <c r="E213" s="9">
-        <f>IF(D213="","",IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D213="","",IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F213" s="9">
-        <f>IF(OR(D213="",H213="",I213=""),0,IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D213="",H213="",I213=""),0,IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G213" s="7" t="n"/>
@@ -30827,7 +31143,7 @@
         <v/>
       </c>
       <c r="K213" s="9">
-        <f>IF(D213="","",IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D213="","",IFERROR(VLOOKUP(D213,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L213" s="9">
@@ -30841,11 +31157,11 @@
       <c r="C214" s="7" t="n"/>
       <c r="D214" s="7" t="n"/>
       <c r="E214" s="9">
-        <f>IF(D214="","",IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D214="","",IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F214" s="9">
-        <f>IF(OR(D214="",H214="",I214=""),0,IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D214="",H214="",I214=""),0,IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G214" s="7" t="n"/>
@@ -30856,7 +31172,7 @@
         <v/>
       </c>
       <c r="K214" s="9">
-        <f>IF(D214="","",IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D214="","",IFERROR(VLOOKUP(D214,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L214" s="9">
@@ -30870,11 +31186,11 @@
       <c r="C215" s="7" t="n"/>
       <c r="D215" s="7" t="n"/>
       <c r="E215" s="9">
-        <f>IF(D215="","",IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D215="","",IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F215" s="9">
-        <f>IF(OR(D215="",H215="",I215=""),0,IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D215="",H215="",I215=""),0,IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G215" s="7" t="n"/>
@@ -30885,7 +31201,7 @@
         <v/>
       </c>
       <c r="K215" s="9">
-        <f>IF(D215="","",IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D215="","",IFERROR(VLOOKUP(D215,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L215" s="9">
@@ -30899,11 +31215,11 @@
       <c r="C216" s="7" t="n"/>
       <c r="D216" s="7" t="n"/>
       <c r="E216" s="9">
-        <f>IF(D216="","",IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D216="","",IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F216" s="9">
-        <f>IF(OR(D216="",H216="",I216=""),0,IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D216="",H216="",I216=""),0,IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G216" s="7" t="n"/>
@@ -30914,7 +31230,7 @@
         <v/>
       </c>
       <c r="K216" s="9">
-        <f>IF(D216="","",IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D216="","",IFERROR(VLOOKUP(D216,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L216" s="9">
@@ -30928,11 +31244,11 @@
       <c r="C217" s="7" t="n"/>
       <c r="D217" s="7" t="n"/>
       <c r="E217" s="9">
-        <f>IF(D217="","",IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D217="","",IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F217" s="9">
-        <f>IF(OR(D217="",H217="",I217=""),0,IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D217="",H217="",I217=""),0,IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G217" s="7" t="n"/>
@@ -30943,7 +31259,7 @@
         <v/>
       </c>
       <c r="K217" s="9">
-        <f>IF(D217="","",IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D217="","",IFERROR(VLOOKUP(D217,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L217" s="9">
@@ -30957,11 +31273,11 @@
       <c r="C218" s="7" t="n"/>
       <c r="D218" s="7" t="n"/>
       <c r="E218" s="9">
-        <f>IF(D218="","",IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D218="","",IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F218" s="9">
-        <f>IF(OR(D218="",H218="",I218=""),0,IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D218="",H218="",I218=""),0,IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G218" s="7" t="n"/>
@@ -30972,7 +31288,7 @@
         <v/>
       </c>
       <c r="K218" s="9">
-        <f>IF(D218="","",IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D218="","",IFERROR(VLOOKUP(D218,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L218" s="9">
@@ -30986,11 +31302,11 @@
       <c r="C219" s="7" t="n"/>
       <c r="D219" s="7" t="n"/>
       <c r="E219" s="9">
-        <f>IF(D219="","",IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D219="","",IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F219" s="9">
-        <f>IF(OR(D219="",H219="",I219=""),0,IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D219="",H219="",I219=""),0,IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G219" s="7" t="n"/>
@@ -31001,7 +31317,7 @@
         <v/>
       </c>
       <c r="K219" s="9">
-        <f>IF(D219="","",IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D219="","",IFERROR(VLOOKUP(D219,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L219" s="9">
@@ -31015,11 +31331,11 @@
       <c r="C220" s="7" t="n"/>
       <c r="D220" s="7" t="n"/>
       <c r="E220" s="9">
-        <f>IF(D220="","",IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D220="","",IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F220" s="9">
-        <f>IF(OR(D220="",H220="",I220=""),0,IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D220="",H220="",I220=""),0,IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G220" s="7" t="n"/>
@@ -31030,7 +31346,7 @@
         <v/>
       </c>
       <c r="K220" s="9">
-        <f>IF(D220="","",IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D220="","",IFERROR(VLOOKUP(D220,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L220" s="9">
@@ -31044,11 +31360,11 @@
       <c r="C221" s="7" t="n"/>
       <c r="D221" s="7" t="n"/>
       <c r="E221" s="9">
-        <f>IF(D221="","",IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D221="","",IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F221" s="9">
-        <f>IF(OR(D221="",H221="",I221=""),0,IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D221="",H221="",I221=""),0,IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G221" s="7" t="n"/>
@@ -31059,7 +31375,7 @@
         <v/>
       </c>
       <c r="K221" s="9">
-        <f>IF(D221="","",IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D221="","",IFERROR(VLOOKUP(D221,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L221" s="9">
@@ -31073,11 +31389,11 @@
       <c r="C222" s="7" t="n"/>
       <c r="D222" s="7" t="n"/>
       <c r="E222" s="9">
-        <f>IF(D222="","",IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D222="","",IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F222" s="9">
-        <f>IF(OR(D222="",H222="",I222=""),0,IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D222="",H222="",I222=""),0,IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G222" s="7" t="n"/>
@@ -31088,7 +31404,7 @@
         <v/>
       </c>
       <c r="K222" s="9">
-        <f>IF(D222="","",IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D222="","",IFERROR(VLOOKUP(D222,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L222" s="9">
@@ -31102,11 +31418,11 @@
       <c r="C223" s="7" t="n"/>
       <c r="D223" s="7" t="n"/>
       <c r="E223" s="9">
-        <f>IF(D223="","",IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D223="","",IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F223" s="9">
-        <f>IF(OR(D223="",H223="",I223=""),0,IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D223="",H223="",I223=""),0,IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G223" s="7" t="n"/>
@@ -31117,7 +31433,7 @@
         <v/>
       </c>
       <c r="K223" s="9">
-        <f>IF(D223="","",IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D223="","",IFERROR(VLOOKUP(D223,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L223" s="9">
@@ -31131,11 +31447,11 @@
       <c r="C224" s="7" t="n"/>
       <c r="D224" s="7" t="n"/>
       <c r="E224" s="9">
-        <f>IF(D224="","",IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D224="","",IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F224" s="9">
-        <f>IF(OR(D224="",H224="",I224=""),0,IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D224="",H224="",I224=""),0,IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G224" s="7" t="n"/>
@@ -31146,7 +31462,7 @@
         <v/>
       </c>
       <c r="K224" s="9">
-        <f>IF(D224="","",IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D224="","",IFERROR(VLOOKUP(D224,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L224" s="9">
@@ -31160,11 +31476,11 @@
       <c r="C225" s="7" t="n"/>
       <c r="D225" s="7" t="n"/>
       <c r="E225" s="9">
-        <f>IF(D225="","",IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D225="","",IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F225" s="9">
-        <f>IF(OR(D225="",H225="",I225=""),0,IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D225="",H225="",I225=""),0,IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G225" s="7" t="n"/>
@@ -31175,7 +31491,7 @@
         <v/>
       </c>
       <c r="K225" s="9">
-        <f>IF(D225="","",IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D225="","",IFERROR(VLOOKUP(D225,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L225" s="9">
@@ -31189,11 +31505,11 @@
       <c r="C226" s="7" t="n"/>
       <c r="D226" s="7" t="n"/>
       <c r="E226" s="9">
-        <f>IF(D226="","",IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D226="","",IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F226" s="9">
-        <f>IF(OR(D226="",H226="",I226=""),0,IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D226="",H226="",I226=""),0,IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G226" s="7" t="n"/>
@@ -31204,7 +31520,7 @@
         <v/>
       </c>
       <c r="K226" s="9">
-        <f>IF(D226="","",IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D226="","",IFERROR(VLOOKUP(D226,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L226" s="9">
@@ -31218,11 +31534,11 @@
       <c r="C227" s="7" t="n"/>
       <c r="D227" s="7" t="n"/>
       <c r="E227" s="9">
-        <f>IF(D227="","",IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D227="","",IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F227" s="9">
-        <f>IF(OR(D227="",H227="",I227=""),0,IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D227="",H227="",I227=""),0,IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G227" s="7" t="n"/>
@@ -31233,7 +31549,7 @@
         <v/>
       </c>
       <c r="K227" s="9">
-        <f>IF(D227="","",IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D227="","",IFERROR(VLOOKUP(D227,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L227" s="9">
@@ -31247,11 +31563,11 @@
       <c r="C228" s="7" t="n"/>
       <c r="D228" s="7" t="n"/>
       <c r="E228" s="9">
-        <f>IF(D228="","",IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D228="","",IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F228" s="9">
-        <f>IF(OR(D228="",H228="",I228=""),0,IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D228="",H228="",I228=""),0,IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G228" s="7" t="n"/>
@@ -31262,7 +31578,7 @@
         <v/>
       </c>
       <c r="K228" s="9">
-        <f>IF(D228="","",IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D228="","",IFERROR(VLOOKUP(D228,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L228" s="9">
@@ -31276,11 +31592,11 @@
       <c r="C229" s="7" t="n"/>
       <c r="D229" s="7" t="n"/>
       <c r="E229" s="9">
-        <f>IF(D229="","",IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D229="","",IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F229" s="9">
-        <f>IF(OR(D229="",H229="",I229=""),0,IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D229="",H229="",I229=""),0,IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G229" s="7" t="n"/>
@@ -31291,7 +31607,7 @@
         <v/>
       </c>
       <c r="K229" s="9">
-        <f>IF(D229="","",IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D229="","",IFERROR(VLOOKUP(D229,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L229" s="9">
@@ -31305,11 +31621,11 @@
       <c r="C230" s="7" t="n"/>
       <c r="D230" s="7" t="n"/>
       <c r="E230" s="9">
-        <f>IF(D230="","",IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D230="","",IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F230" s="9">
-        <f>IF(OR(D230="",H230="",I230=""),0,IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D230="",H230="",I230=""),0,IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G230" s="7" t="n"/>
@@ -31320,7 +31636,7 @@
         <v/>
       </c>
       <c r="K230" s="9">
-        <f>IF(D230="","",IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D230="","",IFERROR(VLOOKUP(D230,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L230" s="9">
@@ -31334,11 +31650,11 @@
       <c r="C231" s="7" t="n"/>
       <c r="D231" s="7" t="n"/>
       <c r="E231" s="9">
-        <f>IF(D231="","",IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D231="","",IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F231" s="9">
-        <f>IF(OR(D231="",H231="",I231=""),0,IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D231="",H231="",I231=""),0,IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G231" s="7" t="n"/>
@@ -31349,7 +31665,7 @@
         <v/>
       </c>
       <c r="K231" s="9">
-        <f>IF(D231="","",IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D231="","",IFERROR(VLOOKUP(D231,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L231" s="9">
@@ -31363,11 +31679,11 @@
       <c r="C232" s="7" t="n"/>
       <c r="D232" s="7" t="n"/>
       <c r="E232" s="9">
-        <f>IF(D232="","",IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D232="","",IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F232" s="9">
-        <f>IF(OR(D232="",H232="",I232=""),0,IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D232="",H232="",I232=""),0,IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G232" s="7" t="n"/>
@@ -31378,7 +31694,7 @@
         <v/>
       </c>
       <c r="K232" s="9">
-        <f>IF(D232="","",IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D232="","",IFERROR(VLOOKUP(D232,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L232" s="9">
@@ -31392,11 +31708,11 @@
       <c r="C233" s="7" t="n"/>
       <c r="D233" s="7" t="n"/>
       <c r="E233" s="9">
-        <f>IF(D233="","",IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D233="","",IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F233" s="9">
-        <f>IF(OR(D233="",H233="",I233=""),0,IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D233="",H233="",I233=""),0,IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G233" s="7" t="n"/>
@@ -31407,7 +31723,7 @@
         <v/>
       </c>
       <c r="K233" s="9">
-        <f>IF(D233="","",IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D233="","",IFERROR(VLOOKUP(D233,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L233" s="9">
@@ -31421,11 +31737,11 @@
       <c r="C234" s="7" t="n"/>
       <c r="D234" s="7" t="n"/>
       <c r="E234" s="9">
-        <f>IF(D234="","",IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D234="","",IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F234" s="9">
-        <f>IF(OR(D234="",H234="",I234=""),0,IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D234="",H234="",I234=""),0,IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G234" s="7" t="n"/>
@@ -31436,7 +31752,7 @@
         <v/>
       </c>
       <c r="K234" s="9">
-        <f>IF(D234="","",IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D234="","",IFERROR(VLOOKUP(D234,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L234" s="9">
@@ -31450,11 +31766,11 @@
       <c r="C235" s="7" t="n"/>
       <c r="D235" s="7" t="n"/>
       <c r="E235" s="9">
-        <f>IF(D235="","",IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D235="","",IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F235" s="9">
-        <f>IF(OR(D235="",H235="",I235=""),0,IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D235="",H235="",I235=""),0,IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G235" s="7" t="n"/>
@@ -31465,7 +31781,7 @@
         <v/>
       </c>
       <c r="K235" s="9">
-        <f>IF(D235="","",IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D235="","",IFERROR(VLOOKUP(D235,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L235" s="9">
@@ -31479,11 +31795,11 @@
       <c r="C236" s="7" t="n"/>
       <c r="D236" s="7" t="n"/>
       <c r="E236" s="9">
-        <f>IF(D236="","",IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D236="","",IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F236" s="9">
-        <f>IF(OR(D236="",H236="",I236=""),0,IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D236="",H236="",I236=""),0,IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G236" s="7" t="n"/>
@@ -31494,7 +31810,7 @@
         <v/>
       </c>
       <c r="K236" s="9">
-        <f>IF(D236="","",IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D236="","",IFERROR(VLOOKUP(D236,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L236" s="9">
@@ -31508,11 +31824,11 @@
       <c r="C237" s="7" t="n"/>
       <c r="D237" s="7" t="n"/>
       <c r="E237" s="9">
-        <f>IF(D237="","",IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D237="","",IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F237" s="9">
-        <f>IF(OR(D237="",H237="",I237=""),0,IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D237="",H237="",I237=""),0,IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G237" s="7" t="n"/>
@@ -31523,7 +31839,7 @@
         <v/>
       </c>
       <c r="K237" s="9">
-        <f>IF(D237="","",IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D237="","",IFERROR(VLOOKUP(D237,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L237" s="9">
@@ -31537,11 +31853,11 @@
       <c r="C238" s="7" t="n"/>
       <c r="D238" s="7" t="n"/>
       <c r="E238" s="9">
-        <f>IF(D238="","",IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D238="","",IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F238" s="9">
-        <f>IF(OR(D238="",H238="",I238=""),0,IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D238="",H238="",I238=""),0,IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G238" s="7" t="n"/>
@@ -31552,7 +31868,7 @@
         <v/>
       </c>
       <c r="K238" s="9">
-        <f>IF(D238="","",IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D238="","",IFERROR(VLOOKUP(D238,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L238" s="9">
@@ -31566,11 +31882,11 @@
       <c r="C239" s="7" t="n"/>
       <c r="D239" s="7" t="n"/>
       <c r="E239" s="9">
-        <f>IF(D239="","",IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D239="","",IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F239" s="9">
-        <f>IF(OR(D239="",H239="",I239=""),0,IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D239="",H239="",I239=""),0,IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G239" s="7" t="n"/>
@@ -31581,7 +31897,7 @@
         <v/>
       </c>
       <c r="K239" s="9">
-        <f>IF(D239="","",IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D239="","",IFERROR(VLOOKUP(D239,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L239" s="9">
@@ -31595,11 +31911,11 @@
       <c r="C240" s="7" t="n"/>
       <c r="D240" s="7" t="n"/>
       <c r="E240" s="9">
-        <f>IF(D240="","",IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D240="","",IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F240" s="9">
-        <f>IF(OR(D240="",H240="",I240=""),0,IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D240="",H240="",I240=""),0,IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G240" s="7" t="n"/>
@@ -31610,7 +31926,7 @@
         <v/>
       </c>
       <c r="K240" s="9">
-        <f>IF(D240="","",IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D240="","",IFERROR(VLOOKUP(D240,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L240" s="9">
@@ -31624,11 +31940,11 @@
       <c r="C241" s="7" t="n"/>
       <c r="D241" s="7" t="n"/>
       <c r="E241" s="9">
-        <f>IF(D241="","",IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D241="","",IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F241" s="9">
-        <f>IF(OR(D241="",H241="",I241=""),0,IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D241="",H241="",I241=""),0,IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G241" s="7" t="n"/>
@@ -31639,7 +31955,7 @@
         <v/>
       </c>
       <c r="K241" s="9">
-        <f>IF(D241="","",IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D241="","",IFERROR(VLOOKUP(D241,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L241" s="9">
@@ -31653,11 +31969,11 @@
       <c r="C242" s="7" t="n"/>
       <c r="D242" s="7" t="n"/>
       <c r="E242" s="9">
-        <f>IF(D242="","",IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D242="","",IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F242" s="9">
-        <f>IF(OR(D242="",H242="",I242=""),0,IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D242="",H242="",I242=""),0,IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G242" s="7" t="n"/>
@@ -31668,7 +31984,7 @@
         <v/>
       </c>
       <c r="K242" s="9">
-        <f>IF(D242="","",IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D242="","",IFERROR(VLOOKUP(D242,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L242" s="9">
@@ -31682,11 +31998,11 @@
       <c r="C243" s="7" t="n"/>
       <c r="D243" s="7" t="n"/>
       <c r="E243" s="9">
-        <f>IF(D243="","",IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D243="","",IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F243" s="9">
-        <f>IF(OR(D243="",H243="",I243=""),0,IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D243="",H243="",I243=""),0,IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G243" s="7" t="n"/>
@@ -31697,7 +32013,7 @@
         <v/>
       </c>
       <c r="K243" s="9">
-        <f>IF(D243="","",IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D243="","",IFERROR(VLOOKUP(D243,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L243" s="9">
@@ -31711,11 +32027,11 @@
       <c r="C244" s="7" t="n"/>
       <c r="D244" s="7" t="n"/>
       <c r="E244" s="9">
-        <f>IF(D244="","",IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D244="","",IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F244" s="9">
-        <f>IF(OR(D244="",H244="",I244=""),0,IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D244="",H244="",I244=""),0,IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G244" s="7" t="n"/>
@@ -31726,7 +32042,7 @@
         <v/>
       </c>
       <c r="K244" s="9">
-        <f>IF(D244="","",IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D244="","",IFERROR(VLOOKUP(D244,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L244" s="9">
@@ -31740,11 +32056,11 @@
       <c r="C245" s="7" t="n"/>
       <c r="D245" s="7" t="n"/>
       <c r="E245" s="9">
-        <f>IF(D245="","",IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D245="","",IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F245" s="9">
-        <f>IF(OR(D245="",H245="",I245=""),0,IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D245="",H245="",I245=""),0,IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G245" s="7" t="n"/>
@@ -31755,7 +32071,7 @@
         <v/>
       </c>
       <c r="K245" s="9">
-        <f>IF(D245="","",IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D245="","",IFERROR(VLOOKUP(D245,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L245" s="9">
@@ -31769,11 +32085,11 @@
       <c r="C246" s="7" t="n"/>
       <c r="D246" s="7" t="n"/>
       <c r="E246" s="9">
-        <f>IF(D246="","",IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D246="","",IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F246" s="9">
-        <f>IF(OR(D246="",H246="",I246=""),0,IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D246="",H246="",I246=""),0,IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G246" s="7" t="n"/>
@@ -31784,7 +32100,7 @@
         <v/>
       </c>
       <c r="K246" s="9">
-        <f>IF(D246="","",IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D246="","",IFERROR(VLOOKUP(D246,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L246" s="9">
@@ -31798,11 +32114,11 @@
       <c r="C247" s="7" t="n"/>
       <c r="D247" s="7" t="n"/>
       <c r="E247" s="9">
-        <f>IF(D247="","",IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D247="","",IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F247" s="9">
-        <f>IF(OR(D247="",H247="",I247=""),0,IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D247="",H247="",I247=""),0,IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G247" s="7" t="n"/>
@@ -31813,7 +32129,7 @@
         <v/>
       </c>
       <c r="K247" s="9">
-        <f>IF(D247="","",IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D247="","",IFERROR(VLOOKUP(D247,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L247" s="9">
@@ -31827,11 +32143,11 @@
       <c r="C248" s="7" t="n"/>
       <c r="D248" s="7" t="n"/>
       <c r="E248" s="9">
-        <f>IF(D248="","",IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D248="","",IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F248" s="9">
-        <f>IF(OR(D248="",H248="",I248=""),0,IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D248="",H248="",I248=""),0,IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G248" s="7" t="n"/>
@@ -31842,7 +32158,7 @@
         <v/>
       </c>
       <c r="K248" s="9">
-        <f>IF(D248="","",IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D248="","",IFERROR(VLOOKUP(D248,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L248" s="9">
@@ -31856,11 +32172,11 @@
       <c r="C249" s="7" t="n"/>
       <c r="D249" s="7" t="n"/>
       <c r="E249" s="9">
-        <f>IF(D249="","",IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D249="","",IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F249" s="9">
-        <f>IF(OR(D249="",H249="",I249=""),0,IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D249="",H249="",I249=""),0,IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G249" s="7" t="n"/>
@@ -31871,7 +32187,7 @@
         <v/>
       </c>
       <c r="K249" s="9">
-        <f>IF(D249="","",IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D249="","",IFERROR(VLOOKUP(D249,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L249" s="9">
@@ -31885,11 +32201,11 @@
       <c r="C250" s="7" t="n"/>
       <c r="D250" s="7" t="n"/>
       <c r="E250" s="9">
-        <f>IF(D250="","",IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D250="","",IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F250" s="9">
-        <f>IF(OR(D250="",H250="",I250=""),0,IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D250="",H250="",I250=""),0,IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G250" s="7" t="n"/>
@@ -31900,7 +32216,7 @@
         <v/>
       </c>
       <c r="K250" s="9">
-        <f>IF(D250="","",IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D250="","",IFERROR(VLOOKUP(D250,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L250" s="9">
@@ -31914,11 +32230,11 @@
       <c r="C251" s="7" t="n"/>
       <c r="D251" s="7" t="n"/>
       <c r="E251" s="9">
-        <f>IF(D251="","",IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D251="","",IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F251" s="9">
-        <f>IF(OR(D251="",H251="",I251=""),0,IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D251="",H251="",I251=""),0,IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G251" s="7" t="n"/>
@@ -31929,7 +32245,7 @@
         <v/>
       </c>
       <c r="K251" s="9">
-        <f>IF(D251="","",IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D251="","",IFERROR(VLOOKUP(D251,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L251" s="9">
@@ -31943,11 +32259,11 @@
       <c r="C252" s="7" t="n"/>
       <c r="D252" s="7" t="n"/>
       <c r="E252" s="9">
-        <f>IF(D252="","",IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D252="","",IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F252" s="9">
-        <f>IF(OR(D252="",H252="",I252=""),0,IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D252="",H252="",I252=""),0,IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G252" s="7" t="n"/>
@@ -31958,7 +32274,7 @@
         <v/>
       </c>
       <c r="K252" s="9">
-        <f>IF(D252="","",IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D252="","",IFERROR(VLOOKUP(D252,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L252" s="9">
@@ -31972,11 +32288,11 @@
       <c r="C253" s="7" t="n"/>
       <c r="D253" s="7" t="n"/>
       <c r="E253" s="9">
-        <f>IF(D253="","",IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D253="","",IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F253" s="9">
-        <f>IF(OR(D253="",H253="",I253=""),0,IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D253="",H253="",I253=""),0,IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G253" s="7" t="n"/>
@@ -31987,7 +32303,7 @@
         <v/>
       </c>
       <c r="K253" s="9">
-        <f>IF(D253="","",IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D253="","",IFERROR(VLOOKUP(D253,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L253" s="9">
@@ -32001,11 +32317,11 @@
       <c r="C254" s="7" t="n"/>
       <c r="D254" s="7" t="n"/>
       <c r="E254" s="9">
-        <f>IF(D254="","",IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D254="","",IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F254" s="9">
-        <f>IF(OR(D254="",H254="",I254=""),0,IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D254="",H254="",I254=""),0,IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G254" s="7" t="n"/>
@@ -32016,7 +32332,7 @@
         <v/>
       </c>
       <c r="K254" s="9">
-        <f>IF(D254="","",IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D254="","",IFERROR(VLOOKUP(D254,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L254" s="9">
@@ -32030,11 +32346,11 @@
       <c r="C255" s="7" t="n"/>
       <c r="D255" s="7" t="n"/>
       <c r="E255" s="9">
-        <f>IF(D255="","",IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D255="","",IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F255" s="9">
-        <f>IF(OR(D255="",H255="",I255=""),0,IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D255="",H255="",I255=""),0,IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G255" s="7" t="n"/>
@@ -32045,7 +32361,7 @@
         <v/>
       </c>
       <c r="K255" s="9">
-        <f>IF(D255="","",IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D255="","",IFERROR(VLOOKUP(D255,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L255" s="9">
@@ -32059,11 +32375,11 @@
       <c r="C256" s="7" t="n"/>
       <c r="D256" s="7" t="n"/>
       <c r="E256" s="9">
-        <f>IF(D256="","",IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D256="","",IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F256" s="9">
-        <f>IF(OR(D256="",H256="",I256=""),0,IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D256="",H256="",I256=""),0,IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G256" s="7" t="n"/>
@@ -32074,7 +32390,7 @@
         <v/>
       </c>
       <c r="K256" s="9">
-        <f>IF(D256="","",IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D256="","",IFERROR(VLOOKUP(D256,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L256" s="9">
@@ -32088,11 +32404,11 @@
       <c r="C257" s="7" t="n"/>
       <c r="D257" s="7" t="n"/>
       <c r="E257" s="9">
-        <f>IF(D257="","",IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D257="","",IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F257" s="9">
-        <f>IF(OR(D257="",H257="",I257=""),0,IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D257="",H257="",I257=""),0,IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G257" s="7" t="n"/>
@@ -32103,7 +32419,7 @@
         <v/>
       </c>
       <c r="K257" s="9">
-        <f>IF(D257="","",IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D257="","",IFERROR(VLOOKUP(D257,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L257" s="9">
@@ -32117,11 +32433,11 @@
       <c r="C258" s="7" t="n"/>
       <c r="D258" s="7" t="n"/>
       <c r="E258" s="9">
-        <f>IF(D258="","",IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D258="","",IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F258" s="9">
-        <f>IF(OR(D258="",H258="",I258=""),0,IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D258="",H258="",I258=""),0,IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G258" s="7" t="n"/>
@@ -32132,7 +32448,7 @@
         <v/>
       </c>
       <c r="K258" s="9">
-        <f>IF(D258="","",IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D258="","",IFERROR(VLOOKUP(D258,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L258" s="9">
@@ -32146,11 +32462,11 @@
       <c r="C259" s="7" t="n"/>
       <c r="D259" s="7" t="n"/>
       <c r="E259" s="9">
-        <f>IF(D259="","",IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D259="","",IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F259" s="9">
-        <f>IF(OR(D259="",H259="",I259=""),0,IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D259="",H259="",I259=""),0,IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G259" s="7" t="n"/>
@@ -32161,7 +32477,7 @@
         <v/>
       </c>
       <c r="K259" s="9">
-        <f>IF(D259="","",IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D259="","",IFERROR(VLOOKUP(D259,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L259" s="9">
@@ -32175,11 +32491,11 @@
       <c r="C260" s="7" t="n"/>
       <c r="D260" s="7" t="n"/>
       <c r="E260" s="9">
-        <f>IF(D260="","",IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D260="","",IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F260" s="9">
-        <f>IF(OR(D260="",H260="",I260=""),0,IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D260="",H260="",I260=""),0,IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G260" s="7" t="n"/>
@@ -32190,7 +32506,7 @@
         <v/>
       </c>
       <c r="K260" s="9">
-        <f>IF(D260="","",IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D260="","",IFERROR(VLOOKUP(D260,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L260" s="9">
@@ -32204,11 +32520,11 @@
       <c r="C261" s="7" t="n"/>
       <c r="D261" s="7" t="n"/>
       <c r="E261" s="9">
-        <f>IF(D261="","",IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D261="","",IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F261" s="9">
-        <f>IF(OR(D261="",H261="",I261=""),0,IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D261="",H261="",I261=""),0,IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G261" s="7" t="n"/>
@@ -32219,7 +32535,7 @@
         <v/>
       </c>
       <c r="K261" s="9">
-        <f>IF(D261="","",IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D261="","",IFERROR(VLOOKUP(D261,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L261" s="9">
@@ -32233,11 +32549,11 @@
       <c r="C262" s="7" t="n"/>
       <c r="D262" s="7" t="n"/>
       <c r="E262" s="9">
-        <f>IF(D262="","",IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D262="","",IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F262" s="9">
-        <f>IF(OR(D262="",H262="",I262=""),0,IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D262="",H262="",I262=""),0,IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G262" s="7" t="n"/>
@@ -32248,7 +32564,7 @@
         <v/>
       </c>
       <c r="K262" s="9">
-        <f>IF(D262="","",IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D262="","",IFERROR(VLOOKUP(D262,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L262" s="9">
@@ -32262,11 +32578,11 @@
       <c r="C263" s="7" t="n"/>
       <c r="D263" s="7" t="n"/>
       <c r="E263" s="9">
-        <f>IF(D263="","",IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D263="","",IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F263" s="9">
-        <f>IF(OR(D263="",H263="",I263=""),0,IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D263="",H263="",I263=""),0,IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G263" s="7" t="n"/>
@@ -32277,7 +32593,7 @@
         <v/>
       </c>
       <c r="K263" s="9">
-        <f>IF(D263="","",IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D263="","",IFERROR(VLOOKUP(D263,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L263" s="9">
@@ -32291,11 +32607,11 @@
       <c r="C264" s="7" t="n"/>
       <c r="D264" s="7" t="n"/>
       <c r="E264" s="9">
-        <f>IF(D264="","",IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D264="","",IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F264" s="9">
-        <f>IF(OR(D264="",H264="",I264=""),0,IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D264="",H264="",I264=""),0,IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G264" s="7" t="n"/>
@@ -32306,7 +32622,7 @@
         <v/>
       </c>
       <c r="K264" s="9">
-        <f>IF(D264="","",IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D264="","",IFERROR(VLOOKUP(D264,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L264" s="9">
@@ -32320,11 +32636,11 @@
       <c r="C265" s="7" t="n"/>
       <c r="D265" s="7" t="n"/>
       <c r="E265" s="9">
-        <f>IF(D265="","",IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D265="","",IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F265" s="9">
-        <f>IF(OR(D265="",H265="",I265=""),0,IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D265="",H265="",I265=""),0,IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G265" s="7" t="n"/>
@@ -32335,7 +32651,7 @@
         <v/>
       </c>
       <c r="K265" s="9">
-        <f>IF(D265="","",IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D265="","",IFERROR(VLOOKUP(D265,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L265" s="9">
@@ -32349,11 +32665,11 @@
       <c r="C266" s="7" t="n"/>
       <c r="D266" s="7" t="n"/>
       <c r="E266" s="9">
-        <f>IF(D266="","",IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D266="","",IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F266" s="9">
-        <f>IF(OR(D266="",H266="",I266=""),0,IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D266="",H266="",I266=""),0,IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G266" s="7" t="n"/>
@@ -32364,7 +32680,7 @@
         <v/>
       </c>
       <c r="K266" s="9">
-        <f>IF(D266="","",IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D266="","",IFERROR(VLOOKUP(D266,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L266" s="9">
@@ -32378,11 +32694,11 @@
       <c r="C267" s="7" t="n"/>
       <c r="D267" s="7" t="n"/>
       <c r="E267" s="9">
-        <f>IF(D267="","",IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D267="","",IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F267" s="9">
-        <f>IF(OR(D267="",H267="",I267=""),0,IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D267="",H267="",I267=""),0,IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G267" s="7" t="n"/>
@@ -32393,7 +32709,7 @@
         <v/>
       </c>
       <c r="K267" s="9">
-        <f>IF(D267="","",IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D267="","",IFERROR(VLOOKUP(D267,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L267" s="9">
@@ -32407,11 +32723,11 @@
       <c r="C268" s="7" t="n"/>
       <c r="D268" s="7" t="n"/>
       <c r="E268" s="9">
-        <f>IF(D268="","",IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D268="","",IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F268" s="9">
-        <f>IF(OR(D268="",H268="",I268=""),0,IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D268="",H268="",I268=""),0,IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G268" s="7" t="n"/>
@@ -32422,7 +32738,7 @@
         <v/>
       </c>
       <c r="K268" s="9">
-        <f>IF(D268="","",IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D268="","",IFERROR(VLOOKUP(D268,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L268" s="9">
@@ -32436,11 +32752,11 @@
       <c r="C269" s="7" t="n"/>
       <c r="D269" s="7" t="n"/>
       <c r="E269" s="9">
-        <f>IF(D269="","",IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D269="","",IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F269" s="9">
-        <f>IF(OR(D269="",H269="",I269=""),0,IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D269="",H269="",I269=""),0,IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G269" s="7" t="n"/>
@@ -32451,7 +32767,7 @@
         <v/>
       </c>
       <c r="K269" s="9">
-        <f>IF(D269="","",IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D269="","",IFERROR(VLOOKUP(D269,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L269" s="9">
@@ -32465,11 +32781,11 @@
       <c r="C270" s="7" t="n"/>
       <c r="D270" s="7" t="n"/>
       <c r="E270" s="9">
-        <f>IF(D270="","",IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D270="","",IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F270" s="9">
-        <f>IF(OR(D270="",H270="",I270=""),0,IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D270="",H270="",I270=""),0,IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G270" s="7" t="n"/>
@@ -32480,7 +32796,7 @@
         <v/>
       </c>
       <c r="K270" s="9">
-        <f>IF(D270="","",IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D270="","",IFERROR(VLOOKUP(D270,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L270" s="9">
@@ -32494,11 +32810,11 @@
       <c r="C271" s="7" t="n"/>
       <c r="D271" s="7" t="n"/>
       <c r="E271" s="9">
-        <f>IF(D271="","",IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D271="","",IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F271" s="9">
-        <f>IF(OR(D271="",H271="",I271=""),0,IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D271="",H271="",I271=""),0,IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G271" s="7" t="n"/>
@@ -32509,7 +32825,7 @@
         <v/>
       </c>
       <c r="K271" s="9">
-        <f>IF(D271="","",IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D271="","",IFERROR(VLOOKUP(D271,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L271" s="9">
@@ -32523,11 +32839,11 @@
       <c r="C272" s="7" t="n"/>
       <c r="D272" s="7" t="n"/>
       <c r="E272" s="9">
-        <f>IF(D272="","",IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D272="","",IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F272" s="9">
-        <f>IF(OR(D272="",H272="",I272=""),0,IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D272="",H272="",I272=""),0,IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G272" s="7" t="n"/>
@@ -32538,7 +32854,7 @@
         <v/>
       </c>
       <c r="K272" s="9">
-        <f>IF(D272="","",IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D272="","",IFERROR(VLOOKUP(D272,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L272" s="9">
@@ -32552,11 +32868,11 @@
       <c r="C273" s="7" t="n"/>
       <c r="D273" s="7" t="n"/>
       <c r="E273" s="9">
-        <f>IF(D273="","",IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D273="","",IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F273" s="9">
-        <f>IF(OR(D273="",H273="",I273=""),0,IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D273="",H273="",I273=""),0,IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G273" s="7" t="n"/>
@@ -32567,7 +32883,7 @@
         <v/>
       </c>
       <c r="K273" s="9">
-        <f>IF(D273="","",IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D273="","",IFERROR(VLOOKUP(D273,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L273" s="9">
@@ -32581,11 +32897,11 @@
       <c r="C274" s="7" t="n"/>
       <c r="D274" s="7" t="n"/>
       <c r="E274" s="9">
-        <f>IF(D274="","",IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D274="","",IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F274" s="9">
-        <f>IF(OR(D274="",H274="",I274=""),0,IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D274="",H274="",I274=""),0,IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G274" s="7" t="n"/>
@@ -32596,7 +32912,7 @@
         <v/>
       </c>
       <c r="K274" s="9">
-        <f>IF(D274="","",IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D274="","",IFERROR(VLOOKUP(D274,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L274" s="9">
@@ -32610,11 +32926,11 @@
       <c r="C275" s="7" t="n"/>
       <c r="D275" s="7" t="n"/>
       <c r="E275" s="9">
-        <f>IF(D275="","",IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D275="","",IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F275" s="9">
-        <f>IF(OR(D275="",H275="",I275=""),0,IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D275="",H275="",I275=""),0,IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G275" s="7" t="n"/>
@@ -32625,7 +32941,7 @@
         <v/>
       </c>
       <c r="K275" s="9">
-        <f>IF(D275="","",IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D275="","",IFERROR(VLOOKUP(D275,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L275" s="9">
@@ -32639,11 +32955,11 @@
       <c r="C276" s="7" t="n"/>
       <c r="D276" s="7" t="n"/>
       <c r="E276" s="9">
-        <f>IF(D276="","",IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D276="","",IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F276" s="9">
-        <f>IF(OR(D276="",H276="",I276=""),0,IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D276="",H276="",I276=""),0,IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G276" s="7" t="n"/>
@@ -32654,7 +32970,7 @@
         <v/>
       </c>
       <c r="K276" s="9">
-        <f>IF(D276="","",IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D276="","",IFERROR(VLOOKUP(D276,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L276" s="9">
@@ -32668,11 +32984,11 @@
       <c r="C277" s="7" t="n"/>
       <c r="D277" s="7" t="n"/>
       <c r="E277" s="9">
-        <f>IF(D277="","",IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D277="","",IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F277" s="9">
-        <f>IF(OR(D277="",H277="",I277=""),0,IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D277="",H277="",I277=""),0,IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G277" s="7" t="n"/>
@@ -32683,7 +32999,7 @@
         <v/>
       </c>
       <c r="K277" s="9">
-        <f>IF(D277="","",IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D277="","",IFERROR(VLOOKUP(D277,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L277" s="9">
@@ -32697,11 +33013,11 @@
       <c r="C278" s="7" t="n"/>
       <c r="D278" s="7" t="n"/>
       <c r="E278" s="9">
-        <f>IF(D278="","",IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D278="","",IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F278" s="9">
-        <f>IF(OR(D278="",H278="",I278=""),0,IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D278="",H278="",I278=""),0,IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G278" s="7" t="n"/>
@@ -32712,7 +33028,7 @@
         <v/>
       </c>
       <c r="K278" s="9">
-        <f>IF(D278="","",IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D278="","",IFERROR(VLOOKUP(D278,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L278" s="9">
@@ -32726,11 +33042,11 @@
       <c r="C279" s="7" t="n"/>
       <c r="D279" s="7" t="n"/>
       <c r="E279" s="9">
-        <f>IF(D279="","",IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D279="","",IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F279" s="9">
-        <f>IF(OR(D279="",H279="",I279=""),0,IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D279="",H279="",I279=""),0,IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G279" s="7" t="n"/>
@@ -32741,7 +33057,7 @@
         <v/>
       </c>
       <c r="K279" s="9">
-        <f>IF(D279="","",IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D279="","",IFERROR(VLOOKUP(D279,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L279" s="9">
@@ -32755,11 +33071,11 @@
       <c r="C280" s="7" t="n"/>
       <c r="D280" s="7" t="n"/>
       <c r="E280" s="9">
-        <f>IF(D280="","",IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D280="","",IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F280" s="9">
-        <f>IF(OR(D280="",H280="",I280=""),0,IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D280="",H280="",I280=""),0,IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G280" s="7" t="n"/>
@@ -32770,7 +33086,7 @@
         <v/>
       </c>
       <c r="K280" s="9">
-        <f>IF(D280="","",IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D280="","",IFERROR(VLOOKUP(D280,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L280" s="9">
@@ -32784,11 +33100,11 @@
       <c r="C281" s="7" t="n"/>
       <c r="D281" s="7" t="n"/>
       <c r="E281" s="9">
-        <f>IF(D281="","",IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D281="","",IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F281" s="9">
-        <f>IF(OR(D281="",H281="",I281=""),0,IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D281="",H281="",I281=""),0,IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G281" s="7" t="n"/>
@@ -32799,7 +33115,7 @@
         <v/>
       </c>
       <c r="K281" s="9">
-        <f>IF(D281="","",IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D281="","",IFERROR(VLOOKUP(D281,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L281" s="9">
@@ -32813,11 +33129,11 @@
       <c r="C282" s="7" t="n"/>
       <c r="D282" s="7" t="n"/>
       <c r="E282" s="9">
-        <f>IF(D282="","",IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D282="","",IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F282" s="9">
-        <f>IF(OR(D282="",H282="",I282=""),0,IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D282="",H282="",I282=""),0,IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G282" s="7" t="n"/>
@@ -32828,7 +33144,7 @@
         <v/>
       </c>
       <c r="K282" s="9">
-        <f>IF(D282="","",IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D282="","",IFERROR(VLOOKUP(D282,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L282" s="9">
@@ -32842,11 +33158,11 @@
       <c r="C283" s="7" t="n"/>
       <c r="D283" s="7" t="n"/>
       <c r="E283" s="9">
-        <f>IF(D283="","",IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D283="","",IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F283" s="9">
-        <f>IF(OR(D283="",H283="",I283=""),0,IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D283="",H283="",I283=""),0,IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G283" s="7" t="n"/>
@@ -32857,7 +33173,7 @@
         <v/>
       </c>
       <c r="K283" s="9">
-        <f>IF(D283="","",IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D283="","",IFERROR(VLOOKUP(D283,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L283" s="9">
@@ -32871,11 +33187,11 @@
       <c r="C284" s="7" t="n"/>
       <c r="D284" s="7" t="n"/>
       <c r="E284" s="9">
-        <f>IF(D284="","",IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D284="","",IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F284" s="9">
-        <f>IF(OR(D284="",H284="",I284=""),0,IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D284="",H284="",I284=""),0,IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G284" s="7" t="n"/>
@@ -32886,7 +33202,7 @@
         <v/>
       </c>
       <c r="K284" s="9">
-        <f>IF(D284="","",IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D284="","",IFERROR(VLOOKUP(D284,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L284" s="9">
@@ -32900,11 +33216,11 @@
       <c r="C285" s="7" t="n"/>
       <c r="D285" s="7" t="n"/>
       <c r="E285" s="9">
-        <f>IF(D285="","",IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D285="","",IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F285" s="9">
-        <f>IF(OR(D285="",H285="",I285=""),0,IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D285="",H285="",I285=""),0,IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G285" s="7" t="n"/>
@@ -32915,7 +33231,7 @@
         <v/>
       </c>
       <c r="K285" s="9">
-        <f>IF(D285="","",IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D285="","",IFERROR(VLOOKUP(D285,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L285" s="9">
@@ -32929,11 +33245,11 @@
       <c r="C286" s="7" t="n"/>
       <c r="D286" s="7" t="n"/>
       <c r="E286" s="9">
-        <f>IF(D286="","",IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D286="","",IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F286" s="9">
-        <f>IF(OR(D286="",H286="",I286=""),0,IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D286="",H286="",I286=""),0,IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G286" s="7" t="n"/>
@@ -32944,7 +33260,7 @@
         <v/>
       </c>
       <c r="K286" s="9">
-        <f>IF(D286="","",IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D286="","",IFERROR(VLOOKUP(D286,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L286" s="9">
@@ -32958,11 +33274,11 @@
       <c r="C287" s="7" t="n"/>
       <c r="D287" s="7" t="n"/>
       <c r="E287" s="9">
-        <f>IF(D287="","",IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D287="","",IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F287" s="9">
-        <f>IF(OR(D287="",H287="",I287=""),0,IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D287="",H287="",I287=""),0,IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G287" s="7" t="n"/>
@@ -32973,7 +33289,7 @@
         <v/>
       </c>
       <c r="K287" s="9">
-        <f>IF(D287="","",IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D287="","",IFERROR(VLOOKUP(D287,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L287" s="9">
@@ -32987,11 +33303,11 @@
       <c r="C288" s="7" t="n"/>
       <c r="D288" s="7" t="n"/>
       <c r="E288" s="9">
-        <f>IF(D288="","",IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D288="","",IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F288" s="9">
-        <f>IF(OR(D288="",H288="",I288=""),0,IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D288="",H288="",I288=""),0,IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G288" s="7" t="n"/>
@@ -33002,7 +33318,7 @@
         <v/>
       </c>
       <c r="K288" s="9">
-        <f>IF(D288="","",IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D288="","",IFERROR(VLOOKUP(D288,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L288" s="9">
@@ -33016,11 +33332,11 @@
       <c r="C289" s="7" t="n"/>
       <c r="D289" s="7" t="n"/>
       <c r="E289" s="9">
-        <f>IF(D289="","",IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D289="","",IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F289" s="9">
-        <f>IF(OR(D289="",H289="",I289=""),0,IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D289="",H289="",I289=""),0,IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G289" s="7" t="n"/>
@@ -33031,7 +33347,7 @@
         <v/>
       </c>
       <c r="K289" s="9">
-        <f>IF(D289="","",IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D289="","",IFERROR(VLOOKUP(D289,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L289" s="9">
@@ -33045,11 +33361,11 @@
       <c r="C290" s="7" t="n"/>
       <c r="D290" s="7" t="n"/>
       <c r="E290" s="9">
-        <f>IF(D290="","",IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D290="","",IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F290" s="9">
-        <f>IF(OR(D290="",H290="",I290=""),0,IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D290="",H290="",I290=""),0,IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G290" s="7" t="n"/>
@@ -33060,7 +33376,7 @@
         <v/>
       </c>
       <c r="K290" s="9">
-        <f>IF(D290="","",IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D290="","",IFERROR(VLOOKUP(D290,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L290" s="9">
@@ -33074,11 +33390,11 @@
       <c r="C291" s="7" t="n"/>
       <c r="D291" s="7" t="n"/>
       <c r="E291" s="9">
-        <f>IF(D291="","",IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D291="","",IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F291" s="9">
-        <f>IF(OR(D291="",H291="",I291=""),0,IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D291="",H291="",I291=""),0,IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G291" s="7" t="n"/>
@@ -33089,7 +33405,7 @@
         <v/>
       </c>
       <c r="K291" s="9">
-        <f>IF(D291="","",IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D291="","",IFERROR(VLOOKUP(D291,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L291" s="9">
@@ -33103,11 +33419,11 @@
       <c r="C292" s="7" t="n"/>
       <c r="D292" s="7" t="n"/>
       <c r="E292" s="9">
-        <f>IF(D292="","",IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D292="","",IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F292" s="9">
-        <f>IF(OR(D292="",H292="",I292=""),0,IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D292="",H292="",I292=""),0,IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G292" s="7" t="n"/>
@@ -33118,7 +33434,7 @@
         <v/>
       </c>
       <c r="K292" s="9">
-        <f>IF(D292="","",IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D292="","",IFERROR(VLOOKUP(D292,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L292" s="9">
@@ -33132,11 +33448,11 @@
       <c r="C293" s="7" t="n"/>
       <c r="D293" s="7" t="n"/>
       <c r="E293" s="9">
-        <f>IF(D293="","",IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D293="","",IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F293" s="9">
-        <f>IF(OR(D293="",H293="",I293=""),0,IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D293="",H293="",I293=""),0,IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G293" s="7" t="n"/>
@@ -33147,7 +33463,7 @@
         <v/>
       </c>
       <c r="K293" s="9">
-        <f>IF(D293="","",IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D293="","",IFERROR(VLOOKUP(D293,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L293" s="9">
@@ -33161,11 +33477,11 @@
       <c r="C294" s="7" t="n"/>
       <c r="D294" s="7" t="n"/>
       <c r="E294" s="9">
-        <f>IF(D294="","",IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D294="","",IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F294" s="9">
-        <f>IF(OR(D294="",H294="",I294=""),0,IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D294="",H294="",I294=""),0,IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G294" s="7" t="n"/>
@@ -33176,7 +33492,7 @@
         <v/>
       </c>
       <c r="K294" s="9">
-        <f>IF(D294="","",IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D294="","",IFERROR(VLOOKUP(D294,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L294" s="9">
@@ -33190,11 +33506,11 @@
       <c r="C295" s="7" t="n"/>
       <c r="D295" s="7" t="n"/>
       <c r="E295" s="9">
-        <f>IF(D295="","",IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D295="","",IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F295" s="9">
-        <f>IF(OR(D295="",H295="",I295=""),0,IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D295="",H295="",I295=""),0,IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G295" s="7" t="n"/>
@@ -33205,7 +33521,7 @@
         <v/>
       </c>
       <c r="K295" s="9">
-        <f>IF(D295="","",IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D295="","",IFERROR(VLOOKUP(D295,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L295" s="9">
@@ -33219,11 +33535,11 @@
       <c r="C296" s="7" t="n"/>
       <c r="D296" s="7" t="n"/>
       <c r="E296" s="9">
-        <f>IF(D296="","",IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D296="","",IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F296" s="9">
-        <f>IF(OR(D296="",H296="",I296=""),0,IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D296="",H296="",I296=""),0,IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G296" s="7" t="n"/>
@@ -33234,7 +33550,7 @@
         <v/>
       </c>
       <c r="K296" s="9">
-        <f>IF(D296="","",IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D296="","",IFERROR(VLOOKUP(D296,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L296" s="9">
@@ -33248,11 +33564,11 @@
       <c r="C297" s="7" t="n"/>
       <c r="D297" s="7" t="n"/>
       <c r="E297" s="9">
-        <f>IF(D297="","",IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D297="","",IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F297" s="9">
-        <f>IF(OR(D297="",H297="",I297=""),0,IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D297="",H297="",I297=""),0,IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G297" s="7" t="n"/>
@@ -33263,7 +33579,7 @@
         <v/>
       </c>
       <c r="K297" s="9">
-        <f>IF(D297="","",IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D297="","",IFERROR(VLOOKUP(D297,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L297" s="9">
@@ -33277,11 +33593,11 @@
       <c r="C298" s="7" t="n"/>
       <c r="D298" s="7" t="n"/>
       <c r="E298" s="9">
-        <f>IF(D298="","",IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D298="","",IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F298" s="9">
-        <f>IF(OR(D298="",H298="",I298=""),0,IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D298="",H298="",I298=""),0,IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G298" s="7" t="n"/>
@@ -33292,7 +33608,7 @@
         <v/>
       </c>
       <c r="K298" s="9">
-        <f>IF(D298="","",IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D298="","",IFERROR(VLOOKUP(D298,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L298" s="9">
@@ -33306,11 +33622,11 @@
       <c r="C299" s="7" t="n"/>
       <c r="D299" s="7" t="n"/>
       <c r="E299" s="9">
-        <f>IF(D299="","",IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D299="","",IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F299" s="9">
-        <f>IF(OR(D299="",H299="",I299=""),0,IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D299="",H299="",I299=""),0,IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G299" s="7" t="n"/>
@@ -33321,7 +33637,7 @@
         <v/>
       </c>
       <c r="K299" s="9">
-        <f>IF(D299="","",IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D299="","",IFERROR(VLOOKUP(D299,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L299" s="9">
@@ -33335,11 +33651,11 @@
       <c r="C300" s="7" t="n"/>
       <c r="D300" s="7" t="n"/>
       <c r="E300" s="9">
-        <f>IF(D300="","",IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D300="","",IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F300" s="9">
-        <f>IF(OR(D300="",H300="",I300=""),0,IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D300="",H300="",I300=""),0,IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G300" s="7" t="n"/>
@@ -33350,7 +33666,7 @@
         <v/>
       </c>
       <c r="K300" s="9">
-        <f>IF(D300="","",IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D300="","",IFERROR(VLOOKUP(D300,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L300" s="9">
@@ -33364,11 +33680,11 @@
       <c r="C301" s="7" t="n"/>
       <c r="D301" s="7" t="n"/>
       <c r="E301" s="9">
-        <f>IF(D301="","",IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D301="","",IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F301" s="9">
-        <f>IF(OR(D301="",H301="",I301=""),0,IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D301="",H301="",I301=""),0,IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G301" s="7" t="n"/>
@@ -33379,7 +33695,7 @@
         <v/>
       </c>
       <c r="K301" s="9">
-        <f>IF(D301="","",IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D301="","",IFERROR(VLOOKUP(D301,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L301" s="9">
@@ -33393,11 +33709,11 @@
       <c r="C302" s="7" t="n"/>
       <c r="D302" s="7" t="n"/>
       <c r="E302" s="9">
-        <f>IF(D302="","",IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D302="","",IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F302" s="9">
-        <f>IF(OR(D302="",H302="",I302=""),0,IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D302="",H302="",I302=""),0,IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G302" s="7" t="n"/>
@@ -33408,7 +33724,7 @@
         <v/>
       </c>
       <c r="K302" s="9">
-        <f>IF(D302="","",IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D302="","",IFERROR(VLOOKUP(D302,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L302" s="9">
@@ -33422,11 +33738,11 @@
       <c r="C303" s="7" t="n"/>
       <c r="D303" s="7" t="n"/>
       <c r="E303" s="9">
-        <f>IF(D303="","",IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$14,2,FALSE),""))</f>
+        <f>IF(D303="","",IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$19,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="F303" s="9">
-        <f>IF(OR(D303="",H303="",I303=""),0,IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$14,3,FALSE),0))</f>
+        <f>IF(OR(D303="",H303="",I303=""),0,IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$19,3,FALSE),0))</f>
         <v/>
       </c>
       <c r="G303" s="7" t="n"/>
@@ -33437,7 +33753,7 @@
         <v/>
       </c>
       <c r="K303" s="9">
-        <f>IF(D303="","",IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$14,4,FALSE),""))</f>
+        <f>IF(D303="","",IFERROR(VLOOKUP(D303,'Trigger Library'!$B$4:$E$19,4,FALSE),""))</f>
         <v/>
       </c>
       <c r="L303" s="9">
@@ -33462,7 +33778,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="D4:D304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Lists!$G$1:$G$10</formula1>
+      <formula1>Lists!$G$1:$G$16</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35716,7 +36032,7 @@
       <formula1>Lists!$A$1:$A$9</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Lists!$G$1:$G$10</formula1>
+      <formula1>Lists!$G$1:$G$16</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -44072,7 +44388,7 @@
         </is>
       </c>
       <c r="J5" s="12">
-        <f>COUNTIFS('Account Tracker'!$P$4:$P$403,"&lt;&gt;",'Account Tracker'!$R$4:$R$403,"")-COUNTIF('Account Tracker'!$P$4:$P$403,"Won")-COUNTIF('Account Tracker'!$P$4:$P$403,"Lost")-COUNTIF('Account Tracker'!$P$4:$P$403,"Disqualified")</f>
+        <f>SUMPRODUCT(('Account Tracker'!$P$4:$P$403&lt;&gt;"")*('Account Tracker'!$R$4:$R$403="")*('Account Tracker'!$P$4:$P$403&lt;&gt;"Won")*('Account Tracker'!$P$4:$P$403&lt;&gt;"Lost")*('Account Tracker'!$P$4:$P$403&lt;&gt;"Disqualified"))</f>
         <v/>
       </c>
     </row>
